--- a/Processed_Catalog.xlsx
+++ b/Processed_Catalog.xlsx
@@ -425,25 +425,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Date of Message</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>File Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Drive Link</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Original Item Description</t>
@@ -466,15 +466,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>(Our Price Rs (A +B)</t>
+          <t>Increaded Price</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Our Price Rs(Round off to neareast divisible by 5)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Modified Item Description</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Extracted Codes (OCR)</t>
         </is>
@@ -483,10 +488,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>IMG-20260310-WA0002.jpg</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
@@ -505,12 +514,15 @@
       <c r="H2" t="n">
         <v>729</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra Combo set* Length- 34Inch Price -729rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I2" t="n">
+        <v>730</v>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra Combo set* Length- 34Inch Price -730rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Code-1110, SAC, M1O4B, N2ZON, 7810044, 8919534, No.3800, 5 A, L34 inch</t>
         </is>
@@ -519,10 +531,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>VID-20260319-WA0044.mp4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
@@ -541,12 +557,15 @@
       <c r="H3" t="n">
         <v>634</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>**1 GM FORMING MAHARAJ KADA* ( Half Kada Adjustable ) Price - 634 rs Each *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+      <c r="I3" t="n">
+        <v>635</v>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>**1 GM FORMING MAHARAJ KADA* ( Half Kada Adjustable ) Price - 635 rs Each *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Code-827, A'C, M9OB, N235N, 8325067, No.9600, 1GM Forming</t>
         </is>
@@ -555,10 +574,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>IMG-20260310-WA0005.jpg</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
@@ -577,12 +600,15 @@
       <c r="H4" t="n">
         <v>608</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING श्री स्वामी समर्थ CHAIN* Length- 24Inch Price -608rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I4" t="n">
+        <v>610</v>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING श्री स्वामी समर्थ CHAIN* Length- 24Inch Price -610rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Code-1161, M86B, N22SN, 8920056, No.6700, CHAIN, L-24 Inch, 7Fef</t>
         </is>
@@ -591,10 +617,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>IMG-20260310-WA0006.jpg</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
@@ -613,12 +643,15 @@
       <c r="H5" t="n">
         <v>338</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>*GOLD PLATED DAILY WEAR WATERPROOF CHAIN* Length - 22 INCH Price - 338 rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+      <c r="I5" t="n">
+        <v>340</v>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>*GOLD PLATED DAILY WEAR WATERPROOF CHAIN* Length - 22 INCH Price - 340 rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Code-1112, M46A:, N125N, 7810034, No.8399, L-22inch</t>
         </is>
@@ -627,10 +660,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>IMG-20260310-WA0007.jpg</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
@@ -649,12 +686,15 @@
       <c r="H6" t="n">
         <v>486</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>*_1 GM Gold plated Gautam Buddh chain _* L-24 inch Price - 486 Rs Free shipping All over India</t>
-        </is>
+      <c r="I6" t="n">
+        <v>485</v>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>*_1 GM Gold plated Gautam Buddh chain _* L-24 inch Price - 485 Rs Free shipping All over India</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>SAT, M68B, N18ON, 9816034, No.3650, L-24 Inch</t>
         </is>
@@ -663,10 +703,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>IMG-20260310-WA0004.jpg</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
@@ -685,12 +729,15 @@
       <c r="H7" t="n">
         <v>338</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>*Premium Quality Micro Gold Shree Swami Samarth Chain* Length- 24Inch *Price -338rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I7" t="n">
+        <v>340</v>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>*Premium Quality Micro Gold Shree Swami Samarth Chain* Length- 24Inch *Price -340rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>M46B, NIZSN, No.5350, L-24inch, Sac</t>
         </is>
@@ -699,10 +746,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>VID-20260310-WA0003.mp4</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
@@ -721,12 +772,15 @@
       <c r="H8" t="n">
         <v>877</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>*1 GM Forming 18k Gold Plated Chain* *Length-22 inch                                           *Price - 877 rs                                               ⭐️ FREE SHIPPING ALL OVER INDIA ⭐️</t>
-        </is>
+      <c r="I8" t="n">
+        <v>875</v>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>*1 GM Forming 18k Gold Plated Chain* *Length-22 inch                                           *Price - 875 rs                                               ⭐️ FREE SHIPPING ALL OVER INDIA ⭐️</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Code-1138, A'C, M124C, N325N, 9340062, No.71400, SAC, L-22 inch, 1GM</t>
         </is>
@@ -735,10 +789,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>IMG-20260311-WA0000.jpg</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
@@ -757,12 +815,15 @@
       <c r="H9" t="n">
         <v>1350</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1350 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Code-1204, SA", L-28 Inch, M194C, NSOON, 8965024, No.81200, Eae)</t>
         </is>
@@ -771,10 +832,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>IMG-20260311-WA0001.jpg</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
@@ -793,12 +858,15 @@
       <c r="H10" t="n">
         <v>1350</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1350 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Code-1205, SAC, M194C, NSOON, 4265077, L-28 Inch, No.91200</t>
         </is>
@@ -807,10 +875,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>VID-20260315-WA0014.mp4</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
@@ -829,12 +901,15 @@
       <c r="H11" t="n">
         <v>931</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -931rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I11" t="n">
+        <v>930</v>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -930rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Code-1207, SAC, M134B, NJASN, 9738056, No.9850, L-36 Inch</t>
         </is>
@@ -843,10 +918,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>VID-20260313-WA0048.mp4</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
@@ -865,12 +944,15 @@
       <c r="H12" t="n">
         <v>931</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -931rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I12" t="n">
+        <v>930</v>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -930rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Code-1207, M134B, N345N, 9738056, No.9850, SAI, L-36 Inch</t>
         </is>
@@ -879,10 +961,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0043.jpg</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
@@ -901,12 +987,15 @@
       <c r="H13" t="n">
         <v>1012</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1012rs *FREE SHIPPING ALL OVER INDIA*</t>
-        </is>
+      <c r="I13" t="n">
+        <v>1010</v>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1010rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Code-1208, SAC, M146B, N375N, 2348056, 2950, L42inch, No:</t>
         </is>
@@ -915,10 +1004,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0046.jpg</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
@@ -937,12 +1030,15 @@
       <c r="H14" t="n">
         <v>1012</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1012rs *FREE SHIPPING ALL OVER INDIA*</t>
-        </is>
+      <c r="I14" t="n">
+        <v>1010</v>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1010rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Code-1209, SAC, M146B, N375N, 2348056, No. 2950, L42 inch</t>
         </is>
@@ -951,10 +1047,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0044.jpg</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
@@ -973,12 +1073,15 @@
       <c r="H15" t="n">
         <v>1012</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1012rs *FREE SHIPPING ALL OVER INDIA*</t>
-        </is>
+      <c r="I15" t="n">
+        <v>1010</v>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1010rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Code-1210, SAC, M146B, N375N, 2348056, No. 2950, L42 inch</t>
         </is>
@@ -987,10 +1090,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0040.jpg</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
@@ -1009,12 +1116,15 @@
       <c r="H16" t="n">
         <v>1012</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1012rs *FREE SHIPPING ALL OVER INDIA*</t>
-        </is>
+      <c r="I16" t="n">
+        <v>1010</v>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>VICTORIAN MANGALSUTRA SET L-42 Inch Price - 1010rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Code-1211, SAC, M146B, N375N, 2348056, No.2950, L42inch</t>
         </is>
@@ -1023,10 +1133,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0047.jpg</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
@@ -1045,12 +1159,15 @@
       <c r="H17" t="n">
         <v>1080</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 1080rs *FREE SHIPPING ALL OVER INDIA*</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Code-1212, SAC, M1S6B, N4OON, 2355045, No 9950, L40 Inch, 5 A</t>
         </is>
@@ -1059,10 +1176,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0045.jpg</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
@@ -1081,12 +1202,15 @@
       <c r="H18" t="n">
         <v>1080</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 1080rs *FREE SHIPPING ALL OVER INDIA*</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Code-1213, SAC, M156B, N4OON, 2355045, No. 9950, L40 Inch</t>
         </is>
@@ -1095,10 +1219,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0039.jpg</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
@@ -1117,12 +1245,15 @@
       <c r="H19" t="n">
         <v>1080</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 1080rs *FREE SHIPPING ALL OVER INDIA*</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Code-1214, SAC, M1S6B, N4OON, 2355045, No. 9950, L40 Inch, 8 A</t>
         </is>
@@ -1131,10 +1262,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0042.jpg</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
@@ -1153,12 +1288,15 @@
       <c r="H20" t="n">
         <v>1080</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 1080rs *FREE SHIPPING ALL OVER INDIA*</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Code-1215, SAC, M156B, N4OON, 2355045, No. 9950, L40 Inch, Long</t>
         </is>
@@ -1167,10 +1305,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0041.jpg</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
@@ -1189,12 +1331,15 @@
       <c r="H21" t="n">
         <v>1080</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 1080rs *FREE SHIPPING ALL OVER INDIA*</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>SAC, Code-1216, M1S6B, N4OON, 2355045, No. 9950, L40 Inch, Long</t>
         </is>
@@ -1203,10 +1348,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0038.jpg</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
@@ -1225,12 +1374,15 @@
       <c r="H22" t="n">
         <v>1080</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 1080rs *FREE SHIPPING ALL OVER INDIA*</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Code-1217, SAC, M1S6B, N4OON, 2355045, No. 9950, L40 Inch</t>
         </is>
@@ -1239,10 +1391,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0037.jpg</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
@@ -1261,12 +1417,15 @@
       <c r="H23" t="n">
         <v>567</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -567rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I23" t="n">
+        <v>565</v>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -565rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Code-1160, SAC, M8OB, N21ON, 7821056, No.8550, L38 inch</t>
         </is>
@@ -1275,10 +1434,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0036.jpg</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
@@ -1297,12 +1460,15 @@
       <c r="H24" t="n">
         <v>770</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>770</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -770rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>MIIOB, Code-1158, N285N, SAC, 8932567, No.7800, Gwi, L38 inch</t>
         </is>
@@ -1311,10 +1477,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0006.jpg</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
@@ -1333,12 +1503,15 @@
       <c r="H25" t="n">
         <v>662</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -662rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I25" t="n">
+        <v>660</v>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -660rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Code-1157, SAC, M9SA, N24SN, 7829056, No.5699, 6 A C, L36 inch</t>
         </is>
@@ -1347,10 +1520,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0035.jpg</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
@@ -1369,12 +1546,15 @@
       <c r="H26" t="n">
         <v>608</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -608rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I26" t="n">
+        <v>610</v>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -610rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Code-1155, M87A., N225N, 7825077, No.8650, L38 inch</t>
         </is>
@@ -1383,10 +1563,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0032.jpg</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
@@ -1405,12 +1589,15 @@
       <c r="H27" t="n">
         <v>742</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -742rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I27" t="n">
+        <v>740</v>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -740rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Code-1154, SAC, M1O6B, N27SN, 8831056, No.9750, L38 inch</t>
         </is>
@@ -1419,10 +1606,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0033.jpg</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
@@ -1441,12 +1632,15 @@
       <c r="H28" t="n">
         <v>648</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -648rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I28" t="n">
+        <v>650</v>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -650rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Code-1153, SAC, M93A, N240N, 6728044, No.8670, L36 inch</t>
         </is>
@@ -1455,10 +1649,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>VID-20260317-WA0035.mp4</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
@@ -1477,12 +1675,15 @@
       <c r="H29" t="n">
         <v>2430</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>2430</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 inch Price - 2430 rs Free shipping All over India</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Code-1218, SAC, M350E, NIOON, 78125078, No.73800, SAG, L-38 Inch</t>
         </is>
@@ -1491,10 +1692,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>VID-20260313-WA0049.mp4</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
@@ -1513,12 +1718,15 @@
       <c r="H30" t="n">
         <v>2430</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>2430</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 inch Price - 2430 rs Free shipping All over India</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Code-1218, M350E, N9OON, 78125078, No.73800, SAC, L-38 Inch</t>
         </is>
@@ -1527,10 +1735,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>VID-20260317-WA0036.mp4</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
@@ -1549,12 +1761,15 @@
       <c r="H31" t="n">
         <v>2970</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>2970</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 inch Price - 2970 rs Free shipping All over India</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Code-1219, SAC, M430E, NIIOON, 89165023, No.85000, L-38 Inch</t>
         </is>
@@ -1563,10 +1778,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>VID-20260318-WA0008.mp4</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
@@ -1585,12 +1804,15 @@
       <c r="H32" t="n">
         <v>2970</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>2970</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 inch Price - 2970 rs Free shipping All over India</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Code-1220, SAC, M430E, NIIOON, 89165023, No.85000, L-38 Inch</t>
         </is>
@@ -1599,10 +1821,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>VID-20260313-WA0034.mp4</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
@@ -1621,12 +1847,15 @@
       <c r="H33" t="n">
         <v>2970</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>2970</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 inch Price - 2970 rs Free shipping All over India</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Code-1220, M430E, NTIOON, 89165023, No.85000, L-38 Inch</t>
         </is>
@@ -1635,10 +1864,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>VID-20260318-WA0007.mp4</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
@@ -1657,12 +1890,15 @@
       <c r="H34" t="n">
         <v>945</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>945</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>*1 GM Forming Short  Mangalsutra* Length -18   Inch Price - 945 RS Free shipping all over India ☺️</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Code-1221, SAC, M136B, N35ON, 8942055, No.81500, 18 Inch</t>
         </is>
@@ -1671,10 +1907,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0031.jpg</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
@@ -1693,12 +1933,15 @@
       <c r="H35" t="n">
         <v>2295</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Code-1256, M334C, N8SON, 34120056, NO. 93200, L38 inch</t>
         </is>
@@ -1707,10 +1950,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0030.jpg</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
@@ -1729,12 +1976,15 @@
       <c r="H36" t="n">
         <v>2565</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>2565</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2565 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Code-1267, SAC, M374C, N9SON, 34140056, NO 93500, L38 inch</t>
         </is>
@@ -1743,10 +1993,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0029.jpg</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
@@ -1765,12 +2019,15 @@
       <c r="H37" t="n">
         <v>1148</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING RAANI HAAR* Length- 28 Inch Price - 1148 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I37" t="n">
+        <v>1150</v>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING RAANI HAAR* Length- 28 Inch Price - 1150 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>SAC, M166B, N42SN, 3250010, No.91500, 5 A, L 28 inch</t>
         </is>
@@ -1779,10 +2036,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0028.jpg</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
@@ -1801,12 +2062,15 @@
       <c r="H38" t="n">
         <v>2565</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>2565</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2565 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Code-1268, SAC, M374C, NOSON, 34140056, NO. 93500, 8 A C, L38 Inch</t>
         </is>
@@ -1815,10 +2079,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0027.jpg</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
@@ -1837,12 +2105,15 @@
       <c r="H39" t="n">
         <v>2295</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Code-1270, SAC, M334C, N8SON, 34120056, NO. 93200, 5 A, L38 inch</t>
         </is>
@@ -1851,10 +2122,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0026.jpg</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
@@ -1873,12 +2148,15 @@
       <c r="H40" t="n">
         <v>2295</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Code-1271, SAC, M334C, N8SON, 34120056, NO. 93200, 5 A C, L38 inch</t>
         </is>
@@ -1887,10 +2165,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0025.jpg</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
@@ -1909,12 +2191,15 @@
       <c r="H41" t="n">
         <v>2295</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Code-1272, SAC, M334C, N8SON, 34120056, NO 93200, 6 A, L38 inch</t>
         </is>
@@ -1923,10 +2208,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0024.jpg</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
@@ -1945,12 +2234,15 @@
       <c r="H42" t="n">
         <v>2295</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Code-1274, SAC, M334C, N8SON, 34120056, No 93200, 5 A C, L38 inch</t>
         </is>
@@ -1959,10 +2251,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0023.jpg</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
@@ -1981,12 +2277,15 @@
       <c r="H43" t="n">
         <v>2295</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Code-1274, SAC, M334C, N8SON, 34120056, No. 93200, L38 inch</t>
         </is>
@@ -1995,10 +2294,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>VID-20260313-WA0022.mp4</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
@@ -2017,12 +2320,15 @@
       <c r="H44" t="n">
         <v>2092</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2092 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I44" t="n">
+        <v>2090</v>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2090 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>JEWELLERY, M3OOD, NTZ5N, 78105089, No.83500, (-38 Inch</t>
         </is>
@@ -2031,10 +2337,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>VID-20260313-WA0021.mp4</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
@@ -2053,12 +2363,15 @@
       <c r="H45" t="n">
         <v>2092</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2092 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I45" t="n">
+        <v>2090</v>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2090 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>SAr, JEWELLERY, MZOOD, NTZSN, 78105067, No.53500, 1-38 Inch</t>
         </is>
@@ -2067,10 +2380,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>VID-20260313-WA0020.mp4</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
@@ -2089,12 +2406,15 @@
       <c r="H46" t="n">
         <v>2092</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2092 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I46" t="n">
+        <v>2090</v>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2090 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>JEWELLERY, MBOOD, NZ75N, 79105066, No.63500, L-38 Inch</t>
         </is>
@@ -2103,10 +2423,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>VID-20260312-WA0004.mp4</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
@@ -2125,12 +2449,15 @@
       <c r="H47" t="n">
         <v>2295</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Code-754, SAC, M330E, NB5ON, 78120046, No.93500, L-38 Inch</t>
         </is>
@@ -2139,10 +2466,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0019.jpg</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
@@ -2161,12 +2492,15 @@
       <c r="H48" t="n">
         <v>662</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra with Extra Locket* Length- 38 Inch Price -662rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I48" t="n">
+        <v>660</v>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra with Extra Locket* Length- 38 Inch Price -660rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Code-1156, SAC, M94B, N24SN, 8921045, No.9700, L-38 inch</t>
         </is>
@@ -2175,10 +2509,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0018.jpg</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
@@ -2197,12 +2535,15 @@
       <c r="H49" t="n">
         <v>486</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -486rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I49" t="n">
+        <v>485</v>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -485rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Code-1131, SAC, T69A., N1SON, 8618063, No.8550, L-38 inch</t>
         </is>
@@ -2211,10 +2552,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0017.jpg</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
@@ -2233,12 +2578,15 @@
       <c r="H50" t="n">
         <v>472</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -472rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I50" t="n">
+        <v>470</v>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -470rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Code-1202, M67B, N175N, 7815034, No.8500, SA@, L-38 Inch</t>
         </is>
@@ -2247,10 +2595,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0016.jpg</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
@@ -2269,12 +2621,15 @@
       <c r="H51" t="n">
         <v>472</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -472rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I51" t="n">
+        <v>470</v>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -470rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Code-1203, M67B, N175N, 7915023, No.8500, L-38 Inch</t>
         </is>
@@ -2283,10 +2638,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0015.jpg</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
@@ -2305,12 +2664,15 @@
       <c r="H52" t="n">
         <v>472</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -472rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I52" t="n">
+        <v>470</v>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -470rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Code-1204, M65A, N1ZON, 7615034, No.9499, L-36 Inch, 77o</t>
         </is>
@@ -2319,10 +2681,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0014.jpg</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
@@ -2341,12 +2707,15 @@
       <c r="H53" t="n">
         <v>500</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>500</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>*Micro Gold Thushi Combo* Price -500 Rs FREE SHIPPING ALL OVER INDIA😍</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>MZOB, Code-781, N18SN, 6712067, 657034, No.8550</t>
         </is>
@@ -2355,10 +2724,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0013.jpg</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
@@ -2377,12 +2750,15 @@
       <c r="H54" t="n">
         <v>513</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>*Premium Quantity Thushi Necklace Combo Set* Price -513 Rs FREE SHIPPING ALL OVER INDIA😍</t>
-        </is>
+      <c r="I54" t="n">
+        <v>515</v>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>*Premium Quantity Thushi Necklace Combo Set* Price -515 Rs FREE SHIPPING ALL OVER INDIA😍</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Code-1221, M72B, N19ON, SAC, 7621045, No.7499, grf</t>
         </is>
@@ -2391,10 +2767,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0012.jpg</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
@@ -2413,12 +2793,15 @@
       <c r="H55" t="n">
         <v>567</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 38Inch Price -567rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I55" t="n">
+        <v>565</v>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 38Inch Price -565rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Code-1266, SAC, MBOB, N21ON, 7822045, No.9550, L38</t>
         </is>
@@ -2427,10 +2810,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0011.jpg</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
@@ -2449,12 +2836,15 @@
       <c r="H56" t="n">
         <v>580</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>580</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>*New Micro Gold  Mangalsutra* Length- 38Inch Price -580rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Code-1267, SAC, M82B, N2ISN, 7823067, No.7600, SA 6, L38</t>
         </is>
@@ -2463,10 +2853,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0010.jpg</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
@@ -2485,12 +2879,15 @@
       <c r="H57" t="n">
         <v>567</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 38Inch Price -567rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I57" t="n">
+        <v>565</v>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 38Inch Price -565rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Code-1268, SAC, MBOB, N21ON, 7822045, No.8550, 6 A C, L38</t>
         </is>
@@ -2499,10 +2896,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0009.jpg</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
@@ -2521,12 +2922,15 @@
       <c r="H58" t="n">
         <v>1080</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>✨1 GM FORMING Lotus NECKLACE ✨ Price -1080 rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Code-1219, MISOE, N4OON, 6544023, No.91000, 5 A €, 1 Gram</t>
         </is>
@@ -2535,10 +2939,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0008.jpg</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
@@ -2557,12 +2965,15 @@
       <c r="H59" t="n">
         <v>2025</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -2025rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Code-1221, SAC, MZ9OE, NZ50N, 79100045, No.53000, L24 inch</t>
         </is>
@@ -2571,10 +2982,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0007.jpg</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
@@ -2593,12 +3008,15 @@
       <c r="H60" t="n">
         <v>2025</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -2025rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Code-1220, SAC, M29OE, NZS0N, 34100067, No.63000, L24inch</t>
         </is>
@@ -2607,10 +3025,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0006.jpg</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
@@ -2629,12 +3051,15 @@
       <c r="H61" t="n">
         <v>662</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -662rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I61" t="n">
+        <v>660</v>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -660rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Code-1157, SAC, M9SA, N24SN, 7829056, No.5699, 6 A C, L36 inch</t>
         </is>
@@ -2643,10 +3068,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>VID-20260313-WA0005.mp4</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
@@ -2665,12 +3094,15 @@
       <c r="H62" t="n">
         <v>526</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -526 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I62" t="n">
+        <v>525</v>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -525 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>Code-1043, SAC, M74B, N19SN, 5620067, No.8499, L-38 inch</t>
         </is>
@@ -2679,10 +3111,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>VID-20260316-WA0042.mp4</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
@@ -2701,12 +3137,15 @@
       <c r="H63" t="n">
         <v>418</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 18 Inch Price -418rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I63" t="n">
+        <v>420</v>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 18 Inch Price -420rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Code-455, SAC, MS8B, N1SSN, 7813056, No.8450, SAC, L-18 Inch</t>
         </is>
@@ -2715,10 +3154,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0040.jpg</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
@@ -2737,12 +3180,15 @@
       <c r="H64" t="n">
         <v>540</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>540</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>*New Micro Gold  Mangalsutra* Length- 36Inch Price -540rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>M76B, Code-1117, NZOON, 7819523, No.8550, L-36 inch</t>
         </is>
@@ -2751,10 +3197,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0039.jpg</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
@@ -2773,12 +3223,15 @@
       <c r="H65" t="n">
         <v>850</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>850</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>*New Micro Gold  Mangalsutra Combo Set * Length- 36Inch Price -850 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>M12OB, N31SN, Code-1118, 7812056, 7319577, No.4899, L-36 inch</t>
         </is>
@@ -2787,10 +3240,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0004.jpg</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
@@ -2809,12 +3266,15 @@
       <c r="H66" t="n">
         <v>837</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra Combo Set* Length- 36 Inch Price -837 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I66" t="n">
+        <v>835</v>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra Combo Set* Length- 36 Inch Price -835 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Code-1119, M12OB, N31ON, 7812056, 6719523, No.7800, L-36 inch</t>
         </is>
@@ -2823,10 +3283,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0037.jpg</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
@@ -2845,12 +3309,15 @@
       <c r="H67" t="n">
         <v>418</v>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>*Premium Quality Micro Gold 1 Line Bormala* Length- 22 Inch Price -418rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I67" t="n">
+        <v>420</v>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>*Premium Quality Micro Gold 1 Line Bormala* Length- 22 Inch Price -420rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>TS8B, Code-1137, NISSN, 8914033, SAC, No.2440, L-22 inch</t>
         </is>
@@ -2859,10 +3326,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0036.jpg</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
@@ -2881,12 +3352,15 @@
       <c r="H68" t="n">
         <v>662</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -662rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I68" t="n">
+        <v>660</v>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -660rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Code-1150, SAC, M94B, N24SN, 7830056, No.6700, L36 inch</t>
         </is>
@@ -2895,10 +3369,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0035.jpg</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
@@ -2917,12 +3395,15 @@
       <c r="H69" t="n">
         <v>756</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price -756rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I69" t="n">
+        <v>755</v>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price -755rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>M1O8B, N28ON, 3420078, No.3900, L - 38Inch</t>
         </is>
@@ -2931,10 +3412,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0003.jpg</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
@@ -2953,12 +3438,15 @@
       <c r="H70" t="n">
         <v>877</v>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 34 Inch Price -877rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I70" t="n">
+        <v>875</v>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 34 Inch Price -875rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>M126B, N325N, 4531067, No.3999, L - 34Inch</t>
         </is>
@@ -2967,10 +3455,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0034.jpg</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
@@ -2989,12 +3481,15 @@
       <c r="H71" t="n">
         <v>1134</v>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -1134rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I71" t="n">
+        <v>1135</v>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -1135rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>M162C, N42ON, 4510067, 4512067, 4535077, No.1380, L - 36Inch</t>
         </is>
@@ -3003,10 +3498,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0036.jpg</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
@@ -3025,12 +3524,15 @@
       <c r="H72" t="n">
         <v>770</v>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>770</v>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -770rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>MIIOB, Code-1158, N285N, SAC, 8932567, No.7800, Gwi, L38 inch</t>
         </is>
@@ -3039,10 +3541,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0033.jpg</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
@@ -3061,12 +3567,15 @@
       <c r="H73" t="n">
         <v>594</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 40Inch Price -594rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I73" t="n">
+        <v>595</v>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 40Inch Price -595rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>Code-1159, M84B, NZOON, 7823588, No.7600, L-40 inch</t>
         </is>
@@ -3075,10 +3584,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>IMG-20260313-WA0037.jpg</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
@@ -3097,12 +3610,15 @@
       <c r="H74" t="n">
         <v>567</v>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -567rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I74" t="n">
+        <v>565</v>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 38Inch Price -565rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>Code-1160, SAC, M8OB, N21ON, 7821056, No.8550, L38 inch</t>
         </is>
@@ -3111,10 +3627,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0005.jpg</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
@@ -3133,12 +3653,15 @@
       <c r="H75" t="n">
         <v>716</v>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>*Premium quality Handmade Nath  Earcuff* *Price -716rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I75" t="n">
+        <v>715</v>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>*Premium quality Handmade Nath  Earcuff* *Price -715rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>M1O2B, Code-1109, N265N, SAC, 8935077, No.6700</t>
         </is>
@@ -3147,10 +3670,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0006.jpg</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
@@ -3169,12 +3696,15 @@
       <c r="H76" t="n">
         <v>418</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>*Premium Quality  Thushi* Price -418 Rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I76" t="n">
+        <v>420</v>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>*Premium Quality  Thushi* Price -420 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Code-914, MGOA, NIS5N, 8916045, No.8420</t>
         </is>
@@ -3183,10 +3713,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0007.jpg</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
@@ -3205,12 +3739,15 @@
       <c r="H77" t="n">
         <v>756</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra Combo Set* Length- 34 Inch Price -756rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I77" t="n">
+        <v>755</v>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra Combo Set* Length- 34 Inch Price -755rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Code-1111, MTOBB, NZ8ON, 7812045, 7819534, No.4800, L34</t>
         </is>
@@ -3219,10 +3756,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0008.jpg</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
@@ -3241,12 +3782,15 @@
       <c r="H78" t="n">
         <v>837</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 36 Inch Price -837rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I78" t="n">
+        <v>835</v>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 36 Inch Price -835rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>M12OB, N31ON, 5625078, No.9750, 4 O, L-36 Inch</t>
         </is>
@@ -3255,10 +3799,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>VID-20260317-WA0029.mp4</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
@@ -3277,12 +3825,15 @@
       <c r="H79" t="n">
         <v>675</v>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>675</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -675rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>A'C, M9TA., NZS0N, 4530067, No.3700, SAC, L-Solnch, MicroGold</t>
         </is>
@@ -3291,10 +3842,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>VID-20260317-WA0030.mp4</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
@@ -3313,12 +3868,15 @@
       <c r="H80" t="n">
         <v>662</v>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36Inch Price -662 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I80" t="n">
+        <v>660</v>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36Inch Price -660 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>M94B, N24SN, 9030058, Nozzoo, SAC, L36Inch</t>
         </is>
@@ -3327,10 +3885,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>VID-20260317-WA0028.mp4</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
@@ -3349,12 +3911,15 @@
       <c r="H81" t="n">
         <v>513</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 34 Inch Price -513rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+      <c r="I81" t="n">
+        <v>515</v>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra Set* Length- 34 Inch Price -515rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>SAC, M7SA:, NI9ON, 3420578, No.7540, SAC, L-34lnch, MicroGold</t>
         </is>
@@ -3363,10 +3928,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>IMG-20260316-WA0032.jpg</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
@@ -3385,12 +3954,15 @@
       <c r="H82" t="n">
         <v>1066</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>✨Premium Quality South Fancy Necklace✨ Price - 1066rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+      <c r="I82" t="n">
+        <v>1065</v>
       </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>✨Premium Quality South Fancy Necklace✨ Price - 1065rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>M154B, N395N, Code-1195, SAC, 7658523, No.81170</t>
         </is>
@@ -3399,10 +3971,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0011.jpg</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
@@ -3421,12 +3997,15 @@
       <c r="H83" t="n">
         <v>1094</v>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>✨Premium Quality South Fancy Necklace✨ Price - 1094rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+      <c r="I83" t="n">
+        <v>1095</v>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>✨Premium Quality South Fancy Necklace✨ Price - 1095rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>Code-1196, M1S8B, N4OSN, SAC, 5461078, No.71250</t>
         </is>
@@ -3435,10 +4014,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>IMG-20260315-WA0010.jpg</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
@@ -3457,12 +4040,15 @@
       <c r="H84" t="n">
         <v>850</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>850</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>✨Premium Quality South Fancy Necklace✨ Price - 850rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>M122B, Code-1198, N315N, 5643078, No.9850</t>
         </is>
@@ -3471,1234 +4057,1460 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IMG-20260315-WA0009.jpg</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0041.jpg</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>*Micro Gold Short Mangalsutra* Length -18  Inch Price -200 Rs Free shipping all over India ☺️</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>270</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>*Micro Gold Short Mangalsutra* Length -18  Inch Price -270 Rs Free shipping all over India ☺️</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Code-1056, M38A, NIOON, 347578, No.250, L-18 Inch</t>
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>M76B, Code-1117, NZOON, SAC, 7819523, No.8550, L-36 inch</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0031.jpg</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0038.jpg</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING BRACELETS * Price - 730 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>255.5</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>985</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING BRACELETS * Price - 985 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>M142B, Code-1241, N36ON, SAC, 6548067, No.61500</t>
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>TS8B, Code-1137, N1SSN, 8914033, N0.2440, 6844d, 1#a, L-22 inch</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0030.jpg</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>IMG-20260315-WA0009.jpg</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>*1 GM FORMING BRACELETS* Price - 750 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Short Mangalsutra* Length -18  Inch Price -200 Rs Free shipping all over India ☺️</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>750</v>
+        <v>200</v>
       </c>
       <c r="F87" t="n">
-        <v>262.5</v>
+        <v>70</v>
       </c>
       <c r="G87" t="n">
-        <v>262</v>
+        <v>70</v>
       </c>
       <c r="H87" t="n">
-        <v>1012</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING BRACELETS* Price - 1012 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>270</v>
+      </c>
+      <c r="I87" t="n">
+        <v>270</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>M146B, Code-1242, N375N, 6749066, No.71200</t>
+          <t>*Micro Gold Short Mangalsutra* Length -18  Inch Price -270 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Code-1056, M38A, NIOON, 347578, No.250, L-18 Inch</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0029.jpg</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0031.jpg</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>*1 GM FORMING BRACELETS* Price - 750 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING BRACELETS * Price - 730 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="F88" t="n">
-        <v>262.5</v>
+        <v>255.5</v>
       </c>
       <c r="G88" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="H88" t="n">
-        <v>1012</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING BRACELETS* Price - 1012 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>985</v>
+      </c>
+      <c r="I88" t="n">
+        <v>985</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Code-1243, SAC, M146B, N375N, 6749067, No.81200</t>
+          <t>*1 GM FORMING BRACELETS * Price - 985 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>M142B, Code-1241, N36ON, SAC, 6548067, No.61500</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0028.jpg</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0030.jpg</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 430rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*1 GM FORMING BRACELETS* Price - 750 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>430</v>
+        <v>750</v>
       </c>
       <c r="F89" t="n">
-        <v>150.5</v>
+        <v>262.5</v>
       </c>
       <c r="G89" t="n">
-        <v>150</v>
+        <v>262</v>
       </c>
       <c r="H89" t="n">
-        <v>580</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 580rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1012</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1010</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Code-1222, M8ZB, N21SN, 8921056, No.9650, 0 0</t>
+          <t>*1 GM FORMING BRACELETS* Price - 1010 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>M146B, Code-1242, N375N, 6749066, No.71200</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0027.jpg</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0029.jpg</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 430rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*1 GM FORMING BRACELETS* Price - 750 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>430</v>
+        <v>750</v>
       </c>
       <c r="F90" t="n">
-        <v>150.5</v>
+        <v>262.5</v>
       </c>
       <c r="G90" t="n">
-        <v>150</v>
+        <v>262</v>
       </c>
       <c r="H90" t="n">
-        <v>580</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 580rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1012</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1010</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Code-1223, M8ZB, N215N, 8921056, No.3650</t>
+          <t>*1 GM FORMING BRACELETS* Price - 1010 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Code-1243, SAC, M146B, N375N, 6749067, No.81200</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0026.jpg</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0028.jpg</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 900rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 430rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>900</v>
+        <v>430</v>
       </c>
       <c r="F91" t="n">
-        <v>315</v>
+        <v>150.5</v>
       </c>
       <c r="G91" t="n">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="H91" t="n">
-        <v>1215</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 1215rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>580</v>
+      </c>
+      <c r="I91" t="n">
+        <v>580</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>M176B, Code-1224, N4SON, 9364067, No.91250</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 580rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Code-1222, M8ZB, N21SN, 8921056, No.9650, 0 0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0025.jpg</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0027.jpg</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 720rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 430rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>720</v>
+        <v>430</v>
       </c>
       <c r="F92" t="n">
-        <v>252</v>
+        <v>150.5</v>
       </c>
       <c r="G92" t="n">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="H92" t="n">
-        <v>972</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 972rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>580</v>
+      </c>
+      <c r="I92" t="n">
+        <v>580</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>M14OB, Code-1225, N360N, 8947024, No.8950</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 580rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Code-1223, M8ZB, N215N, 8921056, No.3650</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0024.jpg</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0026.jpg</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 720rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 900rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="F93" t="n">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="G93" t="n">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="H93" t="n">
-        <v>972</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Short Necklace✨* Price - 972rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1215</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1215</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>M140B, Code-1226, N36ON, 8947023, No.8950</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 1215rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>M176B, Code-1224, N4SON, 9364067, No.91250</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0023.jpg</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0025.jpg</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>*fancy South ring* Price -230rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 720rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>230</v>
+        <v>720</v>
       </c>
       <c r="F94" t="n">
-        <v>80.5</v>
+        <v>252</v>
       </c>
       <c r="G94" t="n">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="H94" t="n">
-        <v>310</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>*fancy South ring* Price -310rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>972</v>
+      </c>
+      <c r="I94" t="n">
+        <v>970</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Code-1227, SAC, M44A, N115N, 198029, No. 4300</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 970rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>M14OB, Code-1225, N360N, 8947024, No.8950</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0022.jpg</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0024.jpg</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>*PREMIUM QUALITY MOTI TOP'S* Price -230rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 720rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>230</v>
+        <v>720</v>
       </c>
       <c r="F95" t="n">
-        <v>80.5</v>
+        <v>252</v>
       </c>
       <c r="G95" t="n">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="H95" t="n">
-        <v>310</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>*PREMIUM QUALITY MOTI TOP'S* Price -310rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>972</v>
+      </c>
+      <c r="I95" t="n">
+        <v>970</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Code-1228, SAC, M4AA, N115N, 198029, No. 4300, Tops</t>
+          <t>*✨Premium Quality Short Necklace✨* Price - 970rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>M140B, Code-1226, N36ON, 8947023, No.8950</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0021.jpg</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0023.jpg</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 880rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*fancy South ring* Price -230rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>880</v>
+        <v>230</v>
       </c>
       <c r="F96" t="n">
-        <v>308</v>
+        <v>80.5</v>
       </c>
       <c r="G96" t="n">
-        <v>308</v>
+        <v>80</v>
       </c>
       <c r="H96" t="n">
-        <v>1188</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 1188rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>310</v>
+      </c>
+      <c r="I96" t="n">
+        <v>310</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Code-1229, SAC, M172B, N44ON, 8961056, No.91250</t>
+          <t>*fancy South ring* Price -310rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Code-1227, SAC, M44A, N115N, 198029, No. 4300</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0020.jpg</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0022.jpg</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>*✨Premium Quality traditional Short  Necklace✨* Price - 330rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*PREMIUM QUALITY MOTI TOP'S* Price -230rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>330</v>
+        <v>230</v>
       </c>
       <c r="F97" t="n">
-        <v>115.5</v>
+        <v>80.5</v>
       </c>
       <c r="G97" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="H97" t="n">
-        <v>445</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality traditional Short  Necklace✨* Price - 445rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>310</v>
+      </c>
+      <c r="I97" t="n">
+        <v>310</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>M63A., Code-1230, SAC, N165N, 8913578, No.9400</t>
+          <t>*PREMIUM QUALITY MOTI TOP'S* Price -310rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Code-1228, SAC, M4AA, N115N, 198029, No. 4300, Tops</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0019.jpg</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0021.jpg</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Traditional Short Necklace✨* Price - 330rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 880rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>330</v>
+        <v>880</v>
       </c>
       <c r="F98" t="n">
-        <v>115.5</v>
+        <v>308</v>
       </c>
       <c r="G98" t="n">
-        <v>115</v>
+        <v>308</v>
       </c>
       <c r="H98" t="n">
-        <v>445</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Traditional Short Necklace✨* Price - 445rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1188</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1190</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>M63A_, N165N, Code-1231, 8913568, No.7400</t>
+          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 1190rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Code-1229, SAC, M172B, N44ON, 8961056, No.91250</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0018.jpg</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0020.jpg</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 830rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality traditional Short  Necklace✨* Price - 330rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>830</v>
+        <v>330</v>
       </c>
       <c r="F99" t="n">
-        <v>290.5</v>
+        <v>115.5</v>
       </c>
       <c r="G99" t="n">
-        <v>290</v>
+        <v>115</v>
       </c>
       <c r="H99" t="n">
-        <v>1120</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 1120rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>445</v>
+      </c>
+      <c r="I99" t="n">
+        <v>445</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Code-1232, SAC, M162B, N41SN, 8956023, No.91150</t>
+          <t>*✨Premium Quality traditional Short  Necklace✨* Price - 445rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>M63A., Code-1230, SAC, N165N, 8913578, No.9400</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0017.jpg</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0019.jpg</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 500rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Traditional Short Necklace✨* Price - 330rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="F100" t="n">
-        <v>175</v>
+        <v>115.5</v>
       </c>
       <c r="G100" t="n">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="H100" t="n">
-        <v>675</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 675rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>445</v>
+      </c>
+      <c r="I100" t="n">
+        <v>445</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Code-1233, M96B, NZS0N, 8927034, No.9600</t>
+          <t>*✨Premium Quality Traditional Short Necklace✨* Price - 445rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>M63A_, N165N, Code-1231, 8913568, No.7400</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VID-20260319-WA0008.mp4</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0018.jpg</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -410rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 830rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>410</v>
+        <v>830</v>
       </c>
       <c r="F101" t="n">
-        <v>143.5</v>
+        <v>290.5</v>
       </c>
       <c r="G101" t="n">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="H101" t="n">
-        <v>554</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -554rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>1120</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1120</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Code-460, SAC, M78B, NZOSN, 7820045, No.9650, SAC, L-38 Inch</t>
+          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 1120rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Code-1232, SAC, M162B, N41SN, 8956023, No.91150</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VID-20260319-WA0009.mp4</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0017.jpg</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -490rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 500rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="F102" t="n">
-        <v>171.5</v>
+        <v>175</v>
       </c>
       <c r="G102" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H102" t="n">
-        <v>662</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -662rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>675</v>
+      </c>
+      <c r="I102" t="n">
+        <v>675</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Code-456, SAC, M9AB, N24SN, 7830056, No.8750, SAC, L-38 Inch</t>
+          <t>*✨Premium Quality AD Stone Short Necklace✨* Price - 675rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Code-1233, M96B, NZS0N, 8927034, No.9600</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IMG-20260317-WA0037.jpg</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>VID-20260319-WA0008.mp4</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -630rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -410rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>630</v>
+        <v>410</v>
       </c>
       <c r="F103" t="n">
-        <v>220.5</v>
+        <v>143.5</v>
       </c>
       <c r="G103" t="n">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="H103" t="n">
-        <v>850</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -850rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>554</v>
+      </c>
+      <c r="I103" t="n">
+        <v>555</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>SAC, M120C, N315N, 658034, 4528067, No.4980, L - 36Inch</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -555rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Code-460, SAC, M78B, NZOSN, 7820045, No.9650, SAC, L-38 Inch</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IMG-20260317-WA0038.jpg</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>VID-20260319-WA0009.mp4</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -730 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -490rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>730</v>
+        <v>490</v>
       </c>
       <c r="F104" t="n">
-        <v>255.5</v>
+        <v>171.5</v>
       </c>
       <c r="G104" t="n">
-        <v>255</v>
+        <v>172</v>
       </c>
       <c r="H104" t="n">
-        <v>985</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -985 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>662</v>
+      </c>
+      <c r="I104" t="n">
+        <v>660</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>SAC, M140C, N365N, 5612075, 4535078, N0.41180, L - 36Inch</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 38 Inch Price -660rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Code-456, SAC, M9AB, N24SN, 7830056, No.8750, SAC, L-38 Inch</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0034.jpg</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IMG-20260317-WA0037.jpg</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -840rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -630rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="F105" t="n">
-        <v>294</v>
+        <v>220.5</v>
       </c>
       <c r="G105" t="n">
-        <v>294</v>
+        <v>220</v>
       </c>
       <c r="H105" t="n">
-        <v>1134</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -1134rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>850</v>
+      </c>
+      <c r="I105" t="n">
+        <v>850</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>M162C, N42ON, 4510067, 4512067, 4535077, No.1380, L - 36Inch</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -850rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>SAC, M120C, N315N, 658034, 4528067, No.4980, L - 36Inch</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IMG-20260317-WA0039.jpg</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>IMG-20260317-WA0038.jpg</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 36 Inch Price -650rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -730 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>650</v>
+        <v>730</v>
       </c>
       <c r="F106" t="n">
-        <v>227.5</v>
+        <v>255.5</v>
       </c>
       <c r="G106" t="n">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="H106" t="n">
-        <v>877</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 36 Inch Price -877rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>985</v>
+      </c>
+      <c r="I106" t="n">
+        <v>985</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Code-852, M126B, N325N, 7816078, 7823567, No.7850, L-36 Inch</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -985 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>SAC, M140C, N365N, 5612075, 4535078, N0.41180, L - 36Inch</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0018.jpg</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0034.jpg</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -360rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -840rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>360</v>
+        <v>840</v>
       </c>
       <c r="F107" t="n">
-        <v>126</v>
+        <v>294</v>
       </c>
       <c r="G107" t="n">
-        <v>126</v>
+        <v>294</v>
       </c>
       <c r="H107" t="n">
-        <v>486</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -486rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>1134</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1135</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Code-1131, SAC, T69A., N1SON, 8618063, No.8550, L-38 inch</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36 Inch Price -1135rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>M162C, N42ON, 4510067, 4512067, 4535077, No.1380, L - 36Inch</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IMG-20260317-WA0040.jpg</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>IMG-20260317-WA0039.jpg</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>*PREMIUM QUALITY RAANI HAR COMBO SET* Length- 26 Inch Price -440rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 36 Inch Price -650rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>440</v>
+        <v>650</v>
       </c>
       <c r="F108" t="n">
-        <v>154</v>
+        <v>227.5</v>
       </c>
       <c r="G108" t="n">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="H108" t="n">
-        <v>594</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>*PREMIUM QUALITY RAANI HAR COMBO SET* Length- 26 Inch Price -594rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>877</v>
+      </c>
+      <c r="I108" t="n">
+        <v>875</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>M84B, N22ON, 4512068, 5612067, No.3580, 823, L-26 Inch</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 36 Inch Price -875rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Code-852, M126B, N325N, 7816078, 7823567, No.7850, L-36 Inch</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IMG-20260317-WA0041.jpg</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0018.jpg</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>*Micro Gold Bormala Thushi Combo Set* Length- 26 Inch Price -400rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -360rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="F109" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G109" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H109" t="n">
-        <v>540</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>*Micro Gold Bormala Thushi Combo Set* Length- 26 Inch Price -540rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>486</v>
+      </c>
+      <c r="I109" t="n">
+        <v>485</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Code-1071, MZ6B, NZOON, 337598, 5612067, No.8550</t>
+          <t>*New Micro Gold  Mangalsutra* Length- 38 Inch Price -485rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Code-1131, SAC, T69A., N1SON, 8618063, No.8550, L-38 inch</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VID-20260317-WA0029.mp4</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IMG-20260317-WA0040.jpg</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -500rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*PREMIUM QUALITY RAANI HAR COMBO SET* Length- 26 Inch Price -440rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="F110" t="n">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="G110" t="n">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="H110" t="n">
-        <v>675</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -675rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>594</v>
+      </c>
+      <c r="I110" t="n">
+        <v>595</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>A'C, M9TA., NZS0N, 4530067, No.3700, SAC, L-Solnch, MicroGold</t>
+          <t>*PREMIUM QUALITY RAANI HAR COMBO SET* Length- 26 Inch Price -595rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>M84B, N22ON, 4512068, 5612067, No.3580, 823, L-26 Inch</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VID-20260317-WA0030.mp4</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>IMG-20260317-WA0041.jpg</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36Inch Price -490 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Bormala Thushi Combo Set* Length- 26 Inch Price -400rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="F111" t="n">
-        <v>171.5</v>
+        <v>140</v>
       </c>
       <c r="G111" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H111" t="n">
-        <v>662</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Combo Set* Length- 36Inch Price -662 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>540</v>
+      </c>
+      <c r="I111" t="n">
+        <v>540</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>M94B, N24SN, 9030058, Nozzoo, SAC, L36Inch</t>
+          <t>*Micro Gold Bormala Thushi Combo Set* Length- 26 Inch Price -540rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Code-1071, MZ6B, NZOON, 337598, 5612067, No.8550</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VID-20260317-WA0028.mp4</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VID-20260317-WA0029.mp4</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 34 Inch Price -380rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -500rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="F112" t="n">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="G112" t="n">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="H112" t="n">
-        <v>513</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra Set* Length- 34 Inch Price -513rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>675</v>
+      </c>
+      <c r="I112" t="n">
+        <v>675</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>SAC, M7SA:, NI9ON, 3420578, No.7540, SAC, L-34lnch, MicroGold</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 36Inch Price -675rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>A'C, M9TA., NZS0N, 4530067, No.3700, SAC, L-Solnch, MicroGold</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0010.jpg</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>VID-20260317-WA0030.mp4</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>*Premium Quality Jondhale Thushi* Price -300 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36Inch Price -490 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>300</v>
+        <v>490</v>
       </c>
       <c r="F113" t="n">
-        <v>105</v>
+        <v>171.5</v>
       </c>
       <c r="G113" t="n">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="H113" t="n">
-        <v>405</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>*Premium Quality Jondhale Thushi* Price -405 Rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>662</v>
+      </c>
+      <c r="I113" t="n">
+        <v>660</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>5614087, No-5350, SAC, TS6B, N1SON), &amp;lza} 321</t>
+          <t>*Micro Gold Mangalsutra Combo Set* Length- 36Inch Price -660 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>M94B, N24SN, 9030058, Nozzoo, SAC, L36Inch</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0011.jpg</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VID-20260317-WA0028.mp4</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-690rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 34 Inch Price -380rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>690</v>
+        <v>380</v>
       </c>
       <c r="F114" t="n">
-        <v>241.5</v>
+        <v>133</v>
       </c>
       <c r="G114" t="n">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="H114" t="n">
-        <v>931</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-931rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>513</v>
+      </c>
+      <c r="I114" t="n">
+        <v>515</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Code-1038, SAC, M132C, N345N, 7618045, 6716089, No.91000, L-38 inch</t>
+          <t>*Micro Gold Mangalsutra Set* Length- 34 Inch Price -515rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>SAC, M7SA:, NI9ON, 3420578, No.7540, SAC, L-34lnch, MicroGold</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0012.jpg</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0010.jpg</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-700 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Premium Quality Jondhale Thushi* Price -300 Rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="F115" t="n">
-        <v>245</v>
+        <v>105</v>
       </c>
       <c r="G115" t="n">
-        <v>245</v>
+        <v>105</v>
       </c>
       <c r="H115" t="n">
-        <v>945</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-945 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>405</v>
+      </c>
+      <c r="I115" t="n">
+        <v>405</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Code-1037, SAC, M134C, N350N, 675078, 6711057, 6729056, No.81000, L38 inch</t>
+          <t>*Premium Quality Jondhale Thushi* Price -405 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>5614087, No-5350, SAC, TS6B, N1SON), &amp;lza} 321</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0013.jpg</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0011.jpg</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-620rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-690rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>620</v>
+        <v>690</v>
       </c>
       <c r="F116" t="n">
-        <v>217</v>
+        <v>241.5</v>
       </c>
       <c r="G116" t="n">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="H116" t="n">
-        <v>837</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-837rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>931</v>
+      </c>
+      <c r="I116" t="n">
+        <v>930</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Code-1036, SAC, M12OB, N31ON, 568039, 335586, 5623589, No.7900, L38 inch</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-930rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Code-1038, SAC, M132C, N345N, 7618045, 6716089, No.91000, L-38 inch</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IMG-20260318-WA0003.jpg</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0012.jpg</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-700 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="F117" t="n">
-        <v>192.5</v>
+        <v>245</v>
       </c>
       <c r="G117" t="n">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="H117" t="n">
-        <v>742</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+        <v>945</v>
+      </c>
+      <c r="I117" t="n">
+        <v>945</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Code-1204, L20, M1O6B, N2Z5N, 7830045, No.6900</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-945 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Code-1037, SAC, M134C, N350N, 675078, 6711057, 6729056, No.81000, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0043.jpg</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0013.jpg</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-620rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>550</v>
+        <v>620</v>
       </c>
       <c r="F118" t="n">
-        <v>192.5</v>
+        <v>217</v>
       </c>
       <c r="G118" t="n">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="H118" t="n">
-        <v>742</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+        <v>837</v>
+      </c>
+      <c r="I118" t="n">
+        <v>835</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Code-1203, L20, M1O6B, N2Z5N, 7830056, No.6900</t>
+          <t>*Micro Gold Mangalsutra combo Set* Length- 38 Inch Price-835rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Code-1036, SAC, M12OB, N31ON, 568039, 335586, 5623589, No.7900, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0042.jpg</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IMG-20260318-WA0003.jpg</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
@@ -4717,24 +5529,31 @@
       <c r="H119" t="n">
         <v>742</v>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I119" t="n">
+        <v>740</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>M1O6B, Code-1302, N2Z5N, 8930055, No.6900, L2O</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Code-1204, L20, M1O6B, N2Z5N, 7830045, No.6900</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0041.jpg</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0043.jpg</t>
+        </is>
+      </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
@@ -4753,24 +5572,31 @@
       <c r="H120" t="n">
         <v>742</v>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I120" t="n">
+        <v>740</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>M1O6B, Code-1301, N2Z5N, 8930056, No.6900, L20</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Code-1203, L20, M1O6B, N2Z5N, 7830056, No.6900</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0040.jpg</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0042.jpg</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
@@ -4789,24 +5615,31 @@
       <c r="H121" t="n">
         <v>742</v>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I121" t="n">
+        <v>740</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Code-1300, M1O6B, N2Z5N, 8930056, No.7900, L20, Gram</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>M1O6B, Code-1302, N2Z5N, 8930055, No.6900, L2O</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0039.jpg</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0041.jpg</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
@@ -4825,24 +5658,31 @@
       <c r="H122" t="n">
         <v>742</v>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I122" t="n">
+        <v>740</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>M1O6B, Code-1299, N2Z5N, SAC, 8930055, No.7900, L2O</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>M1O6B, Code-1301, N2Z5N, 8930056, No.6900, L20</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0038.jpg</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0040.jpg</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
@@ -4861,24 +5701,31 @@
       <c r="H123" t="n">
         <v>742</v>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I123" t="n">
+        <v>740</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Code-1297, M1O6B, N2Z5N, 8930056, No.7900, L2o</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Code-1300, M1O6B, N2Z5N, 8930056, No.7900, L20, Gram</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0037.jpg</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0039.jpg</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
@@ -4897,24 +5744,31 @@
       <c r="H124" t="n">
         <v>742</v>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I124" t="n">
+        <v>740</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Code-1296, L20, M1O6B, N275N, 9030055, No.8900</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>M1O6B, Code-1299, N2Z5N, SAC, 8930055, No.7900, L2O</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0036.jpg</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0038.jpg</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
@@ -4933,24 +5787,31 @@
       <c r="H125" t="n">
         <v>742</v>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I125" t="n">
+        <v>740</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>M1O6B, Code-1293, N275N, SAC, 7830056, No.7900, L2O</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Code-1297, M1O6B, N2Z5N, 8930056, No.7900, L2o</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0035.jpg</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0037.jpg</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
@@ -4969,24 +5830,31 @@
       <c r="H126" t="n">
         <v>742</v>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I126" t="n">
+        <v>740</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>M1O6B, Code-1292, N275N, SAC, 8930057, No.7900, E4e, L20</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Code-1296, L20, M1O6B, N275N, 9030055, No.8900</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0034.jpg</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0036.jpg</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
@@ -5005,1104 +5873,1321 @@
       <c r="H127" t="n">
         <v>742</v>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+      <c r="I127" t="n">
+        <v>740</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Code-1291, M1O6B, N2Z5N, 8930056, No.7900, L2O</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>M1O6B, Code-1293, N275N, SAC, 7830056, No.7900, L2O</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0033.jpg</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0035.jpg</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -1750rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1750</v>
+        <v>550</v>
       </c>
       <c r="F128" t="n">
-        <v>612.5</v>
+        <v>192.5</v>
       </c>
       <c r="G128" t="n">
-        <v>612</v>
+        <v>192</v>
       </c>
       <c r="H128" t="n">
-        <v>2362</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -2362rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>742</v>
+      </c>
+      <c r="I128" t="n">
+        <v>740</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Code-1290, M340E, N875N, 89120056, No.93600, Sa€, L-24 Inch</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>M1O6B, Code-1292, N275N, SAC, 8930057, No.7900, E4e, L20</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0032.jpg</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0034.jpg</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -1600rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1600</v>
+        <v>550</v>
       </c>
       <c r="F129" t="n">
-        <v>560</v>
+        <v>192.5</v>
       </c>
       <c r="G129" t="n">
-        <v>560</v>
+        <v>192</v>
       </c>
       <c r="H129" t="n">
-        <v>2160</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -2160rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>742</v>
+      </c>
+      <c r="I129" t="n">
+        <v>740</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>M310E, Code- 1289, N8OON, 86102056, No.83200, L-24 Inch</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Code-1291, M1O6B, N2Z5N, 8930056, No.7900, L2O</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0031.jpg</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0033.jpg</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
+          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -1750rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>550</v>
+        <v>1750</v>
       </c>
       <c r="F130" t="n">
-        <v>192.5</v>
+        <v>612.5</v>
       </c>
       <c r="G130" t="n">
-        <v>192</v>
+        <v>612</v>
       </c>
       <c r="H130" t="n">
-        <v>742</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+        <v>2362</v>
+      </c>
+      <c r="I130" t="n">
+        <v>2360</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>M1O6B, Code -1288, N2Z5N, SAC, 6830056, No.7900, L20</t>
+          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -2360rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Code-1290, M340E, N875N, 89120056, No.93600, Sa€, L-24 Inch</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0030.jpg</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0032.jpg</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
+          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -1600rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>550</v>
+        <v>1600</v>
       </c>
       <c r="F131" t="n">
-        <v>192.5</v>
+        <v>560</v>
       </c>
       <c r="G131" t="n">
-        <v>192</v>
+        <v>560</v>
       </c>
       <c r="H131" t="n">
-        <v>742</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 742 RS Free shipping all over India ☺️</t>
-        </is>
+        <v>2160</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2160</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>M1O6B, Code-1285, N275N, SAC, 8030056, No.7900, 1 Gram, L2O</t>
+          <t>*1 Gm Forming  chain (men's)** Length- 24 Inch Price -2160rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>M310E, Code- 1289, N8OON, 86102056, No.83200, L-24 Inch</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0028.jpg</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0031.jpg</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>*✨1 GM FORMING SHORT Necklace ✨* Price - 1450rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1450</v>
+        <v>550</v>
       </c>
       <c r="F132" t="n">
-        <v>507.5</v>
+        <v>192.5</v>
       </c>
       <c r="G132" t="n">
-        <v>507</v>
+        <v>192</v>
       </c>
       <c r="H132" t="n">
-        <v>1957</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>*✨1 GM FORMING SHORT Necklace ✨* Price - 1957rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>742</v>
+      </c>
+      <c r="I132" t="n">
+        <v>740</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Code-1234, SAC, M28OE, N72SN, 5784078, No.91650, 049</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>M1O6B, Code -1288, N2Z5N, SAC, 6830056, No.7900, L20</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0027.jpg</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0030.jpg</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>*✨Premium Quality  Rajwadi Mangalsutra ✨* Length - 40 Inch Price - 3800rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 550 RS Free shipping all over India ☺️</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3800</v>
+        <v>550</v>
       </c>
       <c r="F133" t="n">
-        <v>1330</v>
+        <v>192.5</v>
       </c>
       <c r="G133" t="n">
-        <v>1330</v>
+        <v>192</v>
       </c>
       <c r="H133" t="n">
-        <v>5130</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality  Rajwadi Mangalsutra ✨* Length - 40 Inch Price - 5130rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>742</v>
+      </c>
+      <c r="I133" t="n">
+        <v>740</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Code-1235, SAC, M740J, N19OON, 34280056, No.85600, L40 inch</t>
+          <t>*1 GM Forming Short  Mangalsutra* Length -20   Inch Price - 740 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>M1O6B, Code-1285, N275N, SAC, 8030056, No.7900, 1 Gram, L2O</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0026.jpg</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>VID-20260319-WA0029.mp4</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>✨ गुढीपाडव्याच्या हार्दिक शुभेच्छा ✨ नवीन वर्ष, नवीन स्वप्नं, नवीन यशाची सुरुवात! 💫 सोनेरी नात्यांसारखंच तुमचं आयुष्य उजळत राहो 💛 📍Sururarts Creation 📍 Nerul | Panvel | Ghatkopar</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>378</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 378rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>MSAA, Code-1236, N14ON, 7811045, No.9350</t>
+          <t>✨ गुढीपाडव्याच्या हार्दिक शुभेच्छा ✨ नवीन वर्ष, नवीन स्वप्नं, नवीन यशाची सुरुवात! 💫 सोनेरी नात्यांसारखंच तुमचं आयुष्य उजळत राहो 💛 📍Sururarts Creation 📍 Nerul | Panvel | Ghatkopar</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>syrutigts, GUDI, 8108140424</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0025.jpg</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0028.jpg</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨1 GM FORMING SHORT Necklace ✨* Price - 1450rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>280</v>
+        <v>1450</v>
       </c>
       <c r="F135" t="n">
-        <v>98</v>
+        <v>507.4999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>98</v>
+        <v>507</v>
       </c>
       <c r="H135" t="n">
-        <v>378</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 378rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1957</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1955</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Code-1237, SAC, MSAA, N14ON, 8911045, No.8350, 8 A</t>
+          <t>*✨1 GM FORMING SHORT Necklace ✨* Price - 1955rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Code-1234, SAC, M28OE, N72SN, 5784078, No.91650, 049</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0024.jpg</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0027.jpg</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>*✨Premium Quality  BRIDAL SET✨* Length -24 Inch (Adjustable Gonda) Price - 1200rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality  Rajwadi Mangalsutra ✨* Length - 40 Inch Price - 3800rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1200</v>
+        <v>3800</v>
       </c>
       <c r="F136" t="n">
-        <v>420</v>
+        <v>1330</v>
       </c>
       <c r="G136" t="n">
-        <v>420</v>
+        <v>1330</v>
       </c>
       <c r="H136" t="n">
-        <v>1620</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality  BRIDAL SET✨* Length -24 Inch (Adjustable Gonda) Price - 1620rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>5130</v>
+      </c>
+      <c r="I136" t="n">
+        <v>5130</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Code-1238, SAC, M234C, NGOON, 4935067, 8955023, No.81600, 8 A, 36388, L-24 Inch</t>
+          <t>*✨Premium Quality  Rajwadi Mangalsutra ✨* Length - 40 Inch Price - 5130rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Code-1235, SAC, M740J, N19OON, 34280056, No.85600, L40 inch</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0023.jpg</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0026.jpg</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>*✨Premium Quality  BRIDAL SET ✨* Length -24 Inch (Adjustable Gonda) Price - 1200rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="F137" t="n">
-        <v>420</v>
+        <v>98</v>
       </c>
       <c r="G137" t="n">
-        <v>420</v>
+        <v>98</v>
       </c>
       <c r="H137" t="n">
-        <v>1620</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality  BRIDAL SET ✨* Length -24 Inch (Adjustable Gonda) Price - 1620rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>378</v>
+      </c>
+      <c r="I137" t="n">
+        <v>380</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Code-1240, SAC, M234C, N6OON, 8935067, No.81600, 5 A, L-24 Inch</t>
+          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 380rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>MSAA, Code-1236, N14ON, 7811045, No.9350</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0022.jpg</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0025.jpg</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 700rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="F138" t="n">
-        <v>245</v>
+        <v>98</v>
       </c>
       <c r="G138" t="n">
-        <v>245</v>
+        <v>98</v>
       </c>
       <c r="H138" t="n">
-        <v>945</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 945rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>378</v>
+      </c>
+      <c r="I138" t="n">
+        <v>380</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Code-1239, SAC, M136B, N3SON, 7844057, No.7900</t>
+          <t>*✨Premium Quality AD Stone saree Pin✨* Price - 380rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Code-1237, SAC, MSAA, N14ON, 8911045, No.8350, 8 A</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0021.jpg</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0024.jpg</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 770rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality  BRIDAL SET✨* Length -24 Inch (Adjustable Gonda) Price - 1200rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>770</v>
+        <v>1200</v>
       </c>
       <c r="F139" t="n">
-        <v>269.5</v>
+        <v>420</v>
       </c>
       <c r="G139" t="n">
-        <v>270</v>
+        <v>420</v>
       </c>
       <c r="H139" t="n">
-        <v>1040</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1040rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1620</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1620</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Code-1241, SAC, MISOB, N385N, 8945067, No.8950</t>
+          <t>*✨Premium Quality  BRIDAL SET✨* Length -24 Inch (Adjustable Gonda) Price - 1620rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Code-1238, SAC, M234C, NGOON, 4935067, 8955023, No.81600, 8 A, 36388, L-24 Inch</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0020.jpg</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0023.jpg</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 650rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality  BRIDAL SET ✨* Length -24 Inch (Adjustable Gonda) Price - 1200rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F140" t="n">
-        <v>227.5</v>
+        <v>420</v>
       </c>
       <c r="G140" t="n">
-        <v>227</v>
+        <v>420</v>
       </c>
       <c r="H140" t="n">
-        <v>877</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 877rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1620</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1620</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Code-1242, M126B, N325N, 8936034, No.9750</t>
+          <t>*✨Premium Quality  BRIDAL SET ✨* Length -24 Inch (Adjustable Gonda) Price - 1620rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Code-1240, SAC, M234C, N6OON, 8935067, No.81600, 5 A, L-24 Inch</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0019.jpg</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0022.jpg</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1550rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 700rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1550</v>
+        <v>700</v>
       </c>
       <c r="F141" t="n">
-        <v>542.5</v>
+        <v>245</v>
       </c>
       <c r="G141" t="n">
-        <v>542</v>
+        <v>245</v>
       </c>
       <c r="H141" t="n">
-        <v>2092</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 2092rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>945</v>
+      </c>
+      <c r="I141" t="n">
+        <v>945</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Code-1243, SAC, M3O4C, N775N, 89116034, No.92350</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 945rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Code-1239, SAC, M136B, N3SON, 7844057, No.7900</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0018.jpg</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0021.jpg</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1230rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 770rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1230</v>
+        <v>770</v>
       </c>
       <c r="F142" t="n">
-        <v>430.5</v>
+        <v>269.5</v>
       </c>
       <c r="G142" t="n">
-        <v>430</v>
+        <v>270</v>
       </c>
       <c r="H142" t="n">
-        <v>1660</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1660rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1040</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1040</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Code-1244, SAC, M24OC, N615N, 7684066, No.81700</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1040rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Code-1241, SAC, MISOB, N385N, 8945067, No.8950</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0017.jpg</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0020.jpg</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 950rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 650rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>950</v>
+        <v>650</v>
       </c>
       <c r="F143" t="n">
-        <v>332.5</v>
+        <v>227.5</v>
       </c>
       <c r="G143" t="n">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="H143" t="n">
-        <v>1282</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1282rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>877</v>
+      </c>
+      <c r="I143" t="n">
+        <v>875</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Code-1245, SAC, M184C, N475N, 9862045, No.91250</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 875rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Code-1242, M126B, N325N, 8936034, No.9750</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0016.jpg</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0019.jpg</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>*✨ Finger Ring Adjustable ✨* Price - 280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1550rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>280</v>
+        <v>1550</v>
       </c>
       <c r="F144" t="n">
-        <v>98</v>
+        <v>542.5</v>
       </c>
       <c r="G144" t="n">
-        <v>98</v>
+        <v>542</v>
       </c>
       <c r="H144" t="n">
-        <v>378</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>*✨ Finger Ring Adjustable ✨* Price - 378rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>2092</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2090</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>T52B, Code-1246, N14ON, 575087, No-2280, Adjustable</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 2090rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Code-1243, SAC, M3O4C, N775N, 89116034, No.92350</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0015.jpg</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0018.jpg</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>*✨ Finger Ring Adjustable ✨* Price - 250rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1230rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>250</v>
+        <v>1230</v>
       </c>
       <c r="F145" t="n">
-        <v>87.5</v>
+        <v>430.5</v>
       </c>
       <c r="G145" t="n">
-        <v>88</v>
+        <v>430</v>
       </c>
       <c r="H145" t="n">
-        <v>338</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>*✨ Finger Ring Adjustable ✨* Price - 338rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1660</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1660</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>T44C, Code-1247, N125N, SAC, 567087, No-299, Adjustable</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1660rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Code-1244, SAC, M24OC, N615N, 7684066, No.81700</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IMG-20260319-WA0014.jpg</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0017.jpg</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>*✨ Matte South Mangalsutra ✨* Length -24 Inch Price - 320rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 950rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>320</v>
+        <v>950</v>
       </c>
       <c r="F146" t="n">
-        <v>112</v>
+        <v>332.5</v>
       </c>
       <c r="G146" t="n">
-        <v>112</v>
+        <v>332</v>
       </c>
       <c r="H146" t="n">
-        <v>432</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>*✨ Matte South Mangalsutra ✨* Length -24 Inch Price - 432rs *FREE SHIPPING ALL OVER INDIA😊*</t>
-        </is>
+        <v>1282</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1280</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>TS8C}, NI6ON, Code-1248, 5612087, No-6340, {0a, L-24 inch, SAG, SAC, SAC, SAC, SAC, SAC, SAG, SAC, SAC</t>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Code-1245, SAC, M184C, N475N, 9862045, No.91250</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IMG-20260320-WA0001.jpg</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0016.jpg</t>
+        </is>
+      </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -450 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*✨ Finger Ring Adjustable ✨* Price - 280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>450</v>
+        <v>280</v>
       </c>
       <c r="F147" t="n">
-        <v>157.5</v>
+        <v>98</v>
       </c>
       <c r="G147" t="n">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="H147" t="n">
-        <v>608</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -608 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>378</v>
+      </c>
+      <c r="I147" t="n">
+        <v>380</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Code-1101, T84C, N225N, 8425092, No.3599, L-24 inch, Bormal</t>
+          <t>*✨ Finger Ring Adjustable ✨* Price - 380rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>T52B, Code-1246, N14ON, 575087, No-2280, Adjustable</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>IMG-20260320-WA0002.jpg</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0015.jpg</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -450 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*✨ Finger Ring Adjustable ✨* Price - 250rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F148" t="n">
-        <v>157.5</v>
+        <v>87.5</v>
       </c>
       <c r="G148" t="n">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="H148" t="n">
-        <v>608</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -608 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>338</v>
+      </c>
+      <c r="I148" t="n">
+        <v>340</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Code -1102, M84B, N225N, 9625085, No.8599, L-24 inch, 1GM, Mal</t>
+          <t>*✨ Finger Ring Adjustable ✨* Price - 340rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>T44C, Code-1247, N125N, SAC, 567087, No-299, Adjustable</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>IMG-20260320-WA0003.jpg</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>IMG-20260319-WA0014.jpg</t>
+        </is>
+      </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -450 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*✨ Matte South Mangalsutra ✨* Length -24 Inch Price - 320rs *FREE SHIPPING ALL OVER INDIA😊*</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="F149" t="n">
-        <v>157.5</v>
+        <v>112</v>
       </c>
       <c r="G149" t="n">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="H149" t="n">
-        <v>608</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -608 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>432</v>
+      </c>
+      <c r="I149" t="n">
+        <v>430</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Code-1103, M84B, N225N, 9625085, No.8599, L-24inch, 1GM, Bormal</t>
+          <t>*✨ Matte South Mangalsutra ✨* Length -24 Inch Price - 430rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>TS8C}, NI6ON, Code-1248, 5612087, No-6340, {0a, L-24 inch, SAG, SAC, SAC, SAC, SAC, SAC, SAG, SAC, SAC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VID-20260320-WA0004.mp4</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>IMG-20260320-WA0001.jpg</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>*1 GM FORMING 2 Line Poha Har* Length- 28 Inch Price - 580 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -450 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="F150" t="n">
-        <v>203</v>
+        <v>157.5</v>
       </c>
       <c r="G150" t="n">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="H150" t="n">
-        <v>783</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING 2 Line Poha Har* Length- 28 Inch Price - 783 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>608</v>
+      </c>
+      <c r="I150" t="n">
+        <v>610</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Code-759, MIIOC, N29ON, 8621056, No.71200, SAC, L28 inches</t>
+          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -610 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Code-1101, T84C, N225N, 8425092, No.3599, L-24 inch, Bormal</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VID-20260320-WA0005.mp4</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>IMG-20260320-WA0002.jpg</t>
+        </is>
+      </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -690rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -450 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
       <c r="F151" t="n">
-        <v>241.5</v>
+        <v>157.5</v>
       </c>
       <c r="G151" t="n">
-        <v>241</v>
+        <v>158</v>
       </c>
       <c r="H151" t="n">
-        <v>931</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -931rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>608</v>
+      </c>
+      <c r="I151" t="n">
+        <v>610</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Code-1206, M134B, N34SN, 5638067, No.9850, L-38 inch</t>
+          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -610 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Code -1102, M84B, N225N, 9625085, No.8599, L-24 inch, 1GM, Mal</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VID-20260315-WA0014.mp4</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>IMG-20260320-WA0003.jpg</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -690rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -450 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
       <c r="F152" t="n">
-        <v>241.5</v>
+        <v>157.5</v>
       </c>
       <c r="G152" t="n">
-        <v>241</v>
+        <v>158</v>
       </c>
       <c r="H152" t="n">
-        <v>931</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -931rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>608</v>
+      </c>
+      <c r="I152" t="n">
+        <v>610</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Code-1207, SAC, M134B, NJASN, 9738056, No.9850, L-36 Inch</t>
+          <t>*1 GM FORMING FANCY BORMAL* Length- 24 Inch Price -610 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Code-1103, M84B, N225N, 9625085, No.8599, L-24inch, 1GM, Bormal</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IMG-20260311-WA0001.jpg</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>VID-20260320-WA0004.mp4</t>
+        </is>
+      </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1000 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING 2 Line Poha Har* Length- 28 Inch Price - 580 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="F153" t="n">
-        <v>350</v>
+        <v>203</v>
       </c>
       <c r="G153" t="n">
-        <v>350</v>
+        <v>203</v>
       </c>
       <c r="H153" t="n">
-        <v>1350</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1350 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>783</v>
+      </c>
+      <c r="I153" t="n">
+        <v>785</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Code-1205, SAC, M194C, NSOON, 4265077, L-28 Inch, No.91200</t>
+          <t>*1 GM FORMING 2 Line Poha Har* Length- 28 Inch Price - 785 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Code-759, MIIOC, N29ON, 8621056, No.71200, SAC, L28 inches</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IMG-20260311-WA0000.jpg</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>VID-20260320-WA0005.mp4</t>
+        </is>
+      </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1000 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -690rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="F154" t="n">
-        <v>350</v>
+        <v>241.5</v>
       </c>
       <c r="G154" t="n">
-        <v>350</v>
+        <v>241</v>
       </c>
       <c r="H154" t="n">
-        <v>1350</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1350 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>931</v>
+      </c>
+      <c r="I154" t="n">
+        <v>930</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Code-1204, SA", L-28 Inch, M194C, NSOON, 8965024, No.81200, Eae)</t>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -930rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Code-1206, M134B, N34SN, 5638067, No.9850, L-38 inch</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0023.jpg</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>VID-20260315-WA0014.mp4</t>
+        </is>
+      </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1700 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -690rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1700</v>
+        <v>690</v>
       </c>
       <c r="F155" t="n">
-        <v>595</v>
+        <v>241.5</v>
       </c>
       <c r="G155" t="n">
-        <v>595</v>
+        <v>241</v>
       </c>
       <c r="H155" t="n">
-        <v>2295</v>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>931</v>
+      </c>
+      <c r="I155" t="n">
+        <v>930</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Code-1274, SAC, M334C, N8SON, 34120056, No. 93200, L38 inch</t>
+          <t>*New Micro Gold  Mangalsutra* Length- 36 Inch Price -930rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Code-1207, SAC, M134B, NJASN, 9738056, No.9850, L-36 Inch</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0024.jpg</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>IMG-20260311-WA0001.jpg</t>
+        </is>
+      </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1700 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1000 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="F156" t="n">
-        <v>595</v>
+        <v>350</v>
       </c>
       <c r="G156" t="n">
-        <v>595</v>
+        <v>350</v>
       </c>
       <c r="H156" t="n">
-        <v>2295</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>1350</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1350</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Code-1274, SAC, M334C, N8SON, 34120056, No 93200, 5 A C, L38 inch</t>
+          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1350 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Code-1205, SAC, M194C, NSOON, 4265077, L-28 Inch, No.91200</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0025.jpg</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>IMG-20260311-WA0000.jpg</t>
+        </is>
+      </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1700 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1000 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="F157" t="n">
-        <v>595</v>
+        <v>350</v>
       </c>
       <c r="G157" t="n">
-        <v>595</v>
+        <v>350</v>
       </c>
       <c r="H157" t="n">
-        <v>2295</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>1350</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1350</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Code-1272, SAC, M334C, N8SON, 34120056, NO 93200, 6 A, L38 inch</t>
+          <t>*HANDMADE PARIJAATAK COMBO SET* LENGTH - 28 Inch Price -  1350 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Code-1204, SA", L-28 Inch, M194C, NSOON, 8965024, No.81200, Eae)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0027.jpg</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0023.jpg</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
@@ -6121,96 +7206,117 @@
       <c r="H158" t="n">
         <v>2295</v>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I158" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J158" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Code-1270, SAC, M334C, N8SON, 34120056, NO. 93200, 5 A, L38 inch</t>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Code-1274, SAC, M334C, N8SON, 34120056, No. 93200, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0028.jpg</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0024.jpg</t>
+        </is>
+      </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1900 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1700 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="F159" t="n">
-        <v>665</v>
+        <v>595</v>
       </c>
       <c r="G159" t="n">
-        <v>665</v>
+        <v>595</v>
       </c>
       <c r="H159" t="n">
-        <v>2565</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2565 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>2295</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2295</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Code-1268, SAC, M374C, NOSON, 34140056, NO. 93500, 8 A C, L38 Inch</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Code-1274, SAC, M334C, N8SON, 34120056, No 93200, 5 A C, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0030.jpg</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0025.jpg</t>
+        </is>
+      </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1900 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1700 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="F160" t="n">
-        <v>665</v>
+        <v>595</v>
       </c>
       <c r="G160" t="n">
-        <v>665</v>
+        <v>595</v>
       </c>
       <c r="H160" t="n">
-        <v>2565</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2565 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>2295</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2295</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Code-1267, SAC, M374C, N9SON, 34140056, NO 93500, L38 inch</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Code-1272, SAC, M334C, N8SON, 34120056, NO 93200, 6 A, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0031.jpg</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0027.jpg</t>
+        </is>
+      </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
@@ -6229,142 +7335,189 @@
       <c r="H161" t="n">
         <v>2295</v>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J161" t="inlineStr">
         <is>
           <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Code-1256, M334C, N8SON, 34120056, NO. 93200, L38 inch</t>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Code-1270, SAC, M334C, N8SON, 34120056, NO. 93200, 5 A, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>IMG-20260313-WA0029.jpg</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0028.jpg</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>*1 GM FORMING RAANI HAAR* Length- 28 Inch Price - 850 rs FREE SHIPPING ALL OVER INDIA😊</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1900 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>850</v>
+        <v>1900</v>
       </c>
       <c r="F162" t="n">
-        <v>297.5</v>
+        <v>665</v>
       </c>
       <c r="G162" t="n">
-        <v>298</v>
+        <v>665</v>
       </c>
       <c r="H162" t="n">
-        <v>1148</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>*1 GM FORMING RAANI HAAR* Length- 28 Inch Price - 1148 rs FREE SHIPPING ALL OVER INDIA😊</t>
-        </is>
+        <v>2565</v>
+      </c>
+      <c r="I162" t="n">
+        <v>2565</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>SAC, M166B, N42SN, 3250010, No.91500, 5 A, L 28 inch</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2565 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Code-1268, SAC, M374C, NOSON, 34140056, NO. 93500, 8 A C, L38 Inch</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0041.jpg</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0030.jpg</t>
+        </is>
+      </c>
       <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1900 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>665</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>665</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" t="inlineStr"/>
+        <v>2565</v>
+      </c>
+      <c r="I163" t="n">
+        <v>2565</v>
+      </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>M76B, Code-1117, NZOON, SAC, 7819523, No.8550, L-36 inch</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2565 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Code-1267, SAC, M374C, N9SON, 34140056, NO 93500, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>IMG-20260316-WA0038.jpg</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0031.jpg</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 1700 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" t="inlineStr"/>
+        <v>2295</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2295</v>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>TS8B, Code-1137, N1SSN, 8914033, N0.2440, 6844d, 1#a, L-22 inch</t>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 38 Inch Price - 2295 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Code-1256, M334C, N8SON, 34120056, NO. 93200, L38 inch</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>VID-20260319-WA0029.mp4</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>IMG-20260313-WA0029.jpg</t>
+        </is>
+      </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>✨ गुढीपाडव्याच्या हार्दिक शुभेच्छा ✨ नवीन वर्ष, नवीन स्वप्नं, नवीन यशाची सुरुवात! 💫 सोनेरी नात्यांसारखंच तुमचं आयुष्य उजळत राहो 💛 📍Sururarts Creation 📍 Nerul | Panvel | Ghatkopar</t>
+          <t>*1 GM FORMING RAANI HAAR* Length- 28 Inch Price - 850 rs FREE SHIPPING ALL OVER INDIA😊</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>297.5</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>✨ गुढीपाडव्याच्या हार्दिक शुभेच्छा ✨ नवीन वर्ष, नवीन स्वप्नं, नवीन यशाची सुरुवात! 💫 सोनेरी नात्यांसारखंच तुमचं आयुष्य उजळत राहो 💛 📍Sururarts Creation 📍 Nerul | Panvel | Ghatkopar</t>
-        </is>
+        <v>1148</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1150</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>syrutigts, GUDI, 8108140424</t>
+          <t>*1 GM FORMING RAANI HAAR* Length- 28 Inch Price - 1150 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>SAC, M166B, N42SN, 3250010, No.91500, 5 A, L 28 inch</t>
         </is>
       </c>
     </row>

--- a/Processed_Catalog.xlsx
+++ b/Processed_Catalog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:K221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7521,6 +7521,2406 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>VID-20260326-WA0003.mp4</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 36 inch Price - 1400 rs Free shipping All over India</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F166" t="n">
+        <v>489.9999999999999</v>
+      </c>
+      <c r="G166" t="n">
+        <v>490</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1890</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1890</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING MANGALSUTRA* Length- 36 inch Price - 1890 rs Free shipping All over India</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Code-819, SAC, M2ZOE, NZOON, 6789523, No.73000, SAC, L-36 Inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>IMG-20260326-WA0004.jpg</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra Combo Set * Length- 36Inch Price -630 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>630</v>
+      </c>
+      <c r="F167" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="G167" t="n">
+        <v>220</v>
+      </c>
+      <c r="H167" t="n">
+        <v>850</v>
+      </c>
+      <c r="I167" t="n">
+        <v>850</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>*New Micro Gold  Mangalsutra Combo Set * Length- 36Inch Price -850 rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>M12OB, N31SN, Code-1118, 7812056, 7319577, No.4899, L-36 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0021.jpg</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  BRIDAL COMBO SET ✨* Length -24 Inch (Adjustable Gonda) Price - 2650rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2650</v>
+      </c>
+      <c r="F168" t="n">
+        <v>927.4999999999999</v>
+      </c>
+      <c r="G168" t="n">
+        <v>927</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3577</v>
+      </c>
+      <c r="I168" t="n">
+        <v>3575</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  BRIDAL COMBO SET ✨* Length -24 Inch (Adjustable Gonda) Price - 3575rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Code-1249, MS20E, N1325N, 4165097, 1435096, 7455069, 7945842, No.74050</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0020.jpg</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  BRIDAL SET ✨* Length -24 Inch (Adjustable Gonda) Price - 1900rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F169" t="n">
+        <v>665</v>
+      </c>
+      <c r="G169" t="n">
+        <v>665</v>
+      </c>
+      <c r="H169" t="n">
+        <v>2565</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2565</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  BRIDAL SET ✨* Length -24 Inch (Adjustable Gonda) Price - 2565rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Code-1250, M3ZOE, N9SON, 1435096, 7455096, 9645079, No.92700, '90, -24 Inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0022.jpg</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  Rajwadi Bormala ✨* Length -24 Inch (Adjustable Gonda) Price - 720rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>720</v>
+      </c>
+      <c r="F170" t="n">
+        <v>252</v>
+      </c>
+      <c r="G170" t="n">
+        <v>252</v>
+      </c>
+      <c r="H170" t="n">
+        <v>972</v>
+      </c>
+      <c r="I170" t="n">
+        <v>970</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  Rajwadi Bormala ✨* Length -24 Inch (Adjustable Gonda) Price - 970rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Code-1251, M14OB, M36ON, 6945079, No.6950, L-24 Inch, Aueaiahapst, oboisielo</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0019.jpg</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 1050rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F171" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="G171" t="n">
+        <v>368</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1418</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1420</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 1420rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>M2O4C, Code-1252, NS25N, SAC, 7869034, No.91400</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0023.jpg</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHOCKER✨* *{ ADJUSTABLE GONDA }* Price - 650rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>650</v>
+      </c>
+      <c r="F172" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="G172" t="n">
+        <v>227</v>
+      </c>
+      <c r="H172" t="n">
+        <v>877</v>
+      </c>
+      <c r="I172" t="n">
+        <v>875</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHOCKER✨* *{ ADJUSTABLE GONDA }* Price - 875rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>M126B, Code-1253, N325N, 9837045, No.9800</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0016.jpg</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHANDRAKOR NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 650rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>650</v>
+      </c>
+      <c r="F173" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="G173" t="n">
+        <v>227</v>
+      </c>
+      <c r="H173" t="n">
+        <v>877</v>
+      </c>
+      <c r="I173" t="n">
+        <v>875</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHANDRAKOR NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 875rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Code-1254, M126B, N325N, 8931056, No.9750</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0018.jpg</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHANDRAKOR NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 550rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>550</v>
+      </c>
+      <c r="F174" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="G174" t="n">
+        <v>192</v>
+      </c>
+      <c r="H174" t="n">
+        <v>742</v>
+      </c>
+      <c r="I174" t="n">
+        <v>740</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHANDRAKOR NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 740rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Code-1255, M1O6B, N275N, 9628045, No.6700</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0017.jpg</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHANDRAKOR NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 550rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>550</v>
+      </c>
+      <c r="F175" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="G175" t="n">
+        <v>192</v>
+      </c>
+      <c r="H175" t="n">
+        <v>742</v>
+      </c>
+      <c r="I175" t="n">
+        <v>740</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  RAJWADI CHANDRAKOR NECKLACE ✨* *{ ADJUSTABLE GONDA }* Price - 740rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Code-1256, M1O6B, N2Z5N, SAC, 5628034, No.5700</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>VID-20260322-WA0026.mp4</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>*1 GM Forming Short SAYALI  Mangalsutra* Length -22   Inch Price - 870 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>870</v>
+      </c>
+      <c r="F176" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="G176" t="n">
+        <v>304</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1174</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1175</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>*1 GM Forming Short SAYALI  Mangalsutra* Length -22   Inch Price - 1175 RS Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Code-1257, SAC, M1ZOB, N435N, 8960034, No.71800, SAC, L-22 Inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0011.jpg</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी शिंदे शाही तोडे* Size- 2.4, 2.6, 2.8 Price- 2050 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F177" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="G177" t="n">
+        <v>718</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2768</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2770</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी शिंदे शाही तोडे* Size- 2.4, 2.6, 2.8 Price- 2770 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Code-1258, A'C, M404C, N1025N, 47135096, No.92700</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0013.jpg</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी अष्टपैलू बांगड्या combo set* Size- 2.4, 2.6, 2.8 Price- 1800 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F178" t="n">
+        <v>630</v>
+      </c>
+      <c r="G178" t="n">
+        <v>630</v>
+      </c>
+      <c r="H178" t="n">
+        <v>2430</v>
+      </c>
+      <c r="I178" t="n">
+        <v>2430</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी अष्टपैलू बांगड्या combo set* Size- 2.4, 2.6, 2.8 Price- 2430 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Code-1259, SAC, M354C, NIOON, 89120056, No.92400, 8 A, rufaid, dis:i, 3edq _</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0012.jpg</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी शिंदे शाही तोडे BANGLES SET* Size- 2.4, 2.6, 2.8 Price- 1950 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F179" t="n">
+        <v>682.5</v>
+      </c>
+      <c r="G179" t="n">
+        <v>682</v>
+      </c>
+      <c r="H179" t="n">
+        <v>2632</v>
+      </c>
+      <c r="I179" t="n">
+        <v>2630</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी शिंदे शाही तोडे BANGLES SET* Size- 2.4, 2.6, 2.8 Price- 2630 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Code-1260, M384C, N9ZSN, 89130067, No.92600</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0010.jpg</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी गुलाब तोडे* Size- 2.4, 2.6, 2.8 Price- 2050 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F180" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="G180" t="n">
+        <v>718</v>
+      </c>
+      <c r="H180" t="n">
+        <v>2768</v>
+      </c>
+      <c r="I180" t="n">
+        <v>2770</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>*Heritage राजवाडी गुलाब तोडे* Size- 2.4, 2.6, 2.8 Price- 2770 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Code-1251, SAC, M404C, N1O25N, 47134096, No.42680</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0014.jpg</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1000rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F181" t="n">
+        <v>350</v>
+      </c>
+      <c r="G181" t="n">
+        <v>350</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1350</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage Short Necklace ✨* Price - 1350rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Code-1252, M194C, NSOON, 7465097, No.91360, 38e</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>IMG-20260322-WA0015.jpg</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Palakka. Necklace ✨* Length - 22 Inch Price - 350rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>350</v>
+      </c>
+      <c r="F182" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G182" t="n">
+        <v>122</v>
+      </c>
+      <c r="H182" t="n">
+        <v>472</v>
+      </c>
+      <c r="I182" t="n">
+        <v>470</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Palakka. Necklace ✨* Length - 22 Inch Price - 470rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Code-1253, M66B, N17SN, 4516095, No.6450, L22 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0006.jpg</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 620rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>620</v>
+      </c>
+      <c r="F183" t="n">
+        <v>217</v>
+      </c>
+      <c r="G183" t="n">
+        <v>217</v>
+      </c>
+      <c r="H183" t="n">
+        <v>837</v>
+      </c>
+      <c r="I183" t="n">
+        <v>835</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 835rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Code-1254, SAC, M12OB, N31ON, 8940067, No.9750, L40 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0007.jpg</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 620rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>620</v>
+      </c>
+      <c r="F184" t="n">
+        <v>217</v>
+      </c>
+      <c r="G184" t="n">
+        <v>217</v>
+      </c>
+      <c r="H184" t="n">
+        <v>837</v>
+      </c>
+      <c r="I184" t="n">
+        <v>835</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>*VICTORIAN MANGALSUTRA SET* LENGTH - 40 Inch Price - 835rs *FREE SHIPPING ALL OVER INDIA*</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Code-1255, M12OB, N3ION, 8940056, No.8750, 8A C, L40 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0008.jpg</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -340 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>340</v>
+      </c>
+      <c r="F185" t="n">
+        <v>119</v>
+      </c>
+      <c r="G185" t="n">
+        <v>119</v>
+      </c>
+      <c r="H185" t="n">
+        <v>459</v>
+      </c>
+      <c r="I185" t="n">
+        <v>460</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -460 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Code-1256, SAC, M6SA, N17ON, 8917024, No.7450, L2O inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0009.jpg</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -340 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>340</v>
+      </c>
+      <c r="F186" t="n">
+        <v>119</v>
+      </c>
+      <c r="G186" t="n">
+        <v>119</v>
+      </c>
+      <c r="H186" t="n">
+        <v>459</v>
+      </c>
+      <c r="I186" t="n">
+        <v>460</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -460 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Code-1257, SAC, M6SA, N1ZON, 8917024, No7450, L2O inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0010.jpg</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -340 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>340</v>
+      </c>
+      <c r="F187" t="n">
+        <v>119</v>
+      </c>
+      <c r="G187" t="n">
+        <v>119</v>
+      </c>
+      <c r="H187" t="n">
+        <v>459</v>
+      </c>
+      <c r="I187" t="n">
+        <v>460</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -460 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Code-1258, SAC, M6SA, N1ZON, 8917024, No.7450</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0011.jpg</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -315 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>315</v>
+      </c>
+      <c r="F188" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="G188" t="n">
+        <v>110</v>
+      </c>
+      <c r="H188" t="n">
+        <v>425</v>
+      </c>
+      <c r="I188" t="n">
+        <v>425</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>*Micro Gold Short Mangalsutra* Length -20  Inch Price -425 Rs Free shipping all over India ☺️</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Code-1259, SAC, M6OA;, N1S7N, 7814599, No.7400, Sae, L2O inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0012.jpg</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  AD STONE SOUTH CHOCKER✨* *{ ADJUSTABLE GONDA }* Price - 1730rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F189" t="n">
+        <v>605.5</v>
+      </c>
+      <c r="G189" t="n">
+        <v>606</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2336</v>
+      </c>
+      <c r="I189" t="n">
+        <v>2335</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  AD STONE SOUTH CHOCKER✨* *{ ADJUSTABLE GONDA }* Price - 2335rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Code-1260, SAC, M34OC, N865N, 89115067, No.82300</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0013.jpg</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>*Premium quality South Necklace Laxmi Combo Set* *L-22 inch ( Adjustable Gonda) *Price -1600 rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F190" t="n">
+        <v>560</v>
+      </c>
+      <c r="G190" t="n">
+        <v>560</v>
+      </c>
+      <c r="H190" t="n">
+        <v>2160</v>
+      </c>
+      <c r="I190" t="n">
+        <v>2160</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>*Premium quality South Necklace Laxmi Combo Set* *L-22 inch ( Adjustable Gonda) *Price -2160 rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Code-1275, SAC, M314C, NBOON, 34119056, No. 92100, 8 ,</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0014.jpg</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>*Premium quality South Necklace Combo Set* *L-22 inch ( Adjustable Gonda) *Price -1500rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F191" t="n">
+        <v>525</v>
+      </c>
+      <c r="G191" t="n">
+        <v>525</v>
+      </c>
+      <c r="H191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>*Premium quality South Necklace Combo Set* *L-22 inch ( Adjustable Gonda) *Price -2025rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Code-1276, SAC, M294C, NZ50N, 88110056, No.72000</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>IMG-20260324-WA0015.jpg</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>*Premium quality South Necklace Combo Set* *L-22 inch ( Adjustable Gonda) *Price -1670rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F192" t="n">
+        <v>584.5</v>
+      </c>
+      <c r="G192" t="n">
+        <v>584</v>
+      </c>
+      <c r="H192" t="n">
+        <v>2254</v>
+      </c>
+      <c r="I192" t="n">
+        <v>2255</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>*Premium quality South Necklace Combo Set* *L-22 inch ( Adjustable Gonda) *Price -2255rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Code-1277, SAC, M328C, N835N, 86127035, No.92200, 8 A @</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>VID-20260324-WA0016.mp4</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Code-1218, M350E, N9OON, 78125078, No.73800, SAC, L-38 Inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0011.jpg</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage लक्ष्मी माला ✨* Length - 22 Inch Price - 620rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>620</v>
+      </c>
+      <c r="F194" t="n">
+        <v>217</v>
+      </c>
+      <c r="G194" t="n">
+        <v>217</v>
+      </c>
+      <c r="H194" t="n">
+        <v>837</v>
+      </c>
+      <c r="I194" t="n">
+        <v>835</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage लक्ष्मी माला ✨* Length - 22 Inch Price - 835rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>SAC, Code-1261, M12OB, N31ON, 9835078, No.9750, 649, L22 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0012.jpg</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage लक्ष्मी माला ✨* Length - 22 Inch Price - 620rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>620</v>
+      </c>
+      <c r="F195" t="n">
+        <v>217</v>
+      </c>
+      <c r="G195" t="n">
+        <v>217</v>
+      </c>
+      <c r="H195" t="n">
+        <v>837</v>
+      </c>
+      <c r="I195" t="n">
+        <v>835</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage लक्ष्मी माला ✨* Length - 22 Inch Price - 835rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Code-1262, SAC, M12OB, N31ON, 8935067, No.8750, L22 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0013.jpg</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage लक्ष्मी माला ✨* Length - 22 Inch Price - 620rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>620</v>
+      </c>
+      <c r="F196" t="n">
+        <v>217</v>
+      </c>
+      <c r="G196" t="n">
+        <v>217</v>
+      </c>
+      <c r="H196" t="n">
+        <v>837</v>
+      </c>
+      <c r="I196" t="n">
+        <v>835</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage लक्ष्मी माला ✨* Length - 22 Inch Price - 835rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>SAC, Code-1263, M12OB, N31ON, 8935067, No.8750, L22 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0014.jpg</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage मोती माला ✨* Length - 22 Inch Price - 950rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>950</v>
+      </c>
+      <c r="F197" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="G197" t="n">
+        <v>332</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1282</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1280</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Heritage मोती माला ✨* Length - 22 Inch Price - 1280rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Code-1264, SAC, M186B, N475N, 2368034, No.91350</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0015.jpg</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING KOLI CHRISTIAN  LONG NECKLACE* LENGTH - 40 Inch Price - 2600rs *FREE SHIPPING ALL OVER INDIA😍</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F198" t="n">
+        <v>909.9999999999999</v>
+      </c>
+      <c r="G198" t="n">
+        <v>910</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3510</v>
+      </c>
+      <c r="I198" t="n">
+        <v>3510</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>*1 GM FORMING KOLI CHRISTIAN  LONG NECKLACE* LENGTH - 40 Inch Price - 3510rs *FREE SHIPPING ALL OVER INDIA😍</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>MS1OE, Code-1265, N130ON, SAC, 89200067, No.85500, L30 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0016.jpg</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  BRIDAL SET ✨* Length -30 Inch (Adjustable Gonda) Price - 2000 rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F199" t="n">
+        <v>700</v>
+      </c>
+      <c r="G199" t="n">
+        <v>700</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I199" t="n">
+        <v>2700</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality  BRIDAL SET ✨* Length -30 Inch (Adjustable Gonda) Price - 2700 rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Code-1266, SAC, M39OE, N1OOON, 5648023, 6791034, No.92750, 8 A, L3O inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0017.jpg</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 38 Inch Price -490rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>490</v>
+      </c>
+      <c r="F200" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="G200" t="n">
+        <v>172</v>
+      </c>
+      <c r="H200" t="n">
+        <v>662</v>
+      </c>
+      <c r="I200" t="n">
+        <v>660</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 38 Inch Price -660rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Code-1267, SAC, M94B, N245N, 7429074, No.4700, L38 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0018.jpg</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 40 Inch Price -580rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>580</v>
+      </c>
+      <c r="F201" t="n">
+        <v>203</v>
+      </c>
+      <c r="G201" t="n">
+        <v>203</v>
+      </c>
+      <c r="H201" t="n">
+        <v>783</v>
+      </c>
+      <c r="I201" t="n">
+        <v>785</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 40 Inch Price -785rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>M1 12B, Code-1268, SAC, NZ9ON, 5629074, No.9800, L 40 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0019.jpg</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 40 Inch Price -460rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>460</v>
+      </c>
+      <c r="F202" t="n">
+        <v>161</v>
+      </c>
+      <c r="G202" t="n">
+        <v>161</v>
+      </c>
+      <c r="H202" t="n">
+        <v>621</v>
+      </c>
+      <c r="I202" t="n">
+        <v>620</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 40 Inch Price -620rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Code-1269, SAC, MB8B, N230N, 5824096, No.4700, L40 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0020.jpg</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 36 Inch Price -650rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>650</v>
+      </c>
+      <c r="F203" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="G203" t="n">
+        <v>227</v>
+      </c>
+      <c r="H203" t="n">
+        <v>877</v>
+      </c>
+      <c r="I203" t="n">
+        <v>875</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 36 Inch Price -875rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>M126B, Code-1270, SAC, M325N, 9435096, No.5800, 8 A, L36 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0021.jpg</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 38 Inch Price -570rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>570</v>
+      </c>
+      <c r="F204" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="G204" t="n">
+        <v>200</v>
+      </c>
+      <c r="H204" t="n">
+        <v>770</v>
+      </c>
+      <c r="I204" t="n">
+        <v>770</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>*Micro Gold Mangalsutra* Length- 38 Inch Price -770rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>M11OB, Code-1271, N285N, SAC, 5830096, No.6750, L38 inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0022.jpg</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>*✨MINIMAL TRADITIONAL SHORT NECKLACE* Price - 330rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>330</v>
+      </c>
+      <c r="F205" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="G205" t="n">
+        <v>115</v>
+      </c>
+      <c r="H205" t="n">
+        <v>445</v>
+      </c>
+      <c r="I205" t="n">
+        <v>445</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>*✨MINIMAL TRADITIONAL SHORT NECKLACE* Price - 445rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Code-1272, A'C, M62B, N165N, 8911045, No.9400, (549</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0023.jpg</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>*✨MINIMAL TRADITIONAL SHORT NECKLACE* Price - 330rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>330</v>
+      </c>
+      <c r="F206" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="G206" t="n">
+        <v>115</v>
+      </c>
+      <c r="H206" t="n">
+        <v>445</v>
+      </c>
+      <c r="I206" t="n">
+        <v>445</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>*✨MINIMAL TRADITIONAL SHORT NECKLACE* Price - 445rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Code-1273, M62B, N162N, 8911045, No.9400, SAe</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0024.jpg</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>*Premium Quality Micro Gold 2 Line Bormala* Length- 30 Inch Price -440rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>440</v>
+      </c>
+      <c r="F207" t="n">
+        <v>154</v>
+      </c>
+      <c r="G207" t="n">
+        <v>154</v>
+      </c>
+      <c r="H207" t="n">
+        <v>594</v>
+      </c>
+      <c r="I207" t="n">
+        <v>595</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>*Premium Quality Micro Gold 2 Line Bormala* Length- 30 Inch Price -595rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Code-1274, SAC, M84B, N22ON, 8922059, No.9550, L-30 Inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0025.jpg</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>*Premium Quality Micro Gold 3  Line Bormala* Length- 22 Inch Price -530rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>530</v>
+      </c>
+      <c r="F208" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="G208" t="n">
+        <v>186</v>
+      </c>
+      <c r="H208" t="n">
+        <v>716</v>
+      </c>
+      <c r="I208" t="n">
+        <v>715</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>*Premium Quality Micro Gold 3  Line Bormala* Length- 22 Inch Price -715rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Code-1275, SAC, M1O2B, N265N, 6728045, No.9650, L-30 Inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0026.jpg</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>‼️‼️Stock out‼️‼️</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>‼️‼️Stock out‼️‼️</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Code-1241, SAC, MISOB, N385N, 8945067, No.8950</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0027.jpg</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Palakka. Necklace ✨* Length - 22 Inch Price - 350rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>350</v>
+      </c>
+      <c r="F210" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G210" t="n">
+        <v>122</v>
+      </c>
+      <c r="H210" t="n">
+        <v>472</v>
+      </c>
+      <c r="I210" t="n">
+        <v>470</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>*✨Premium Quality Palakka. Necklace ✨* Length - 22 Inch Price - 470rs *FREE SHIPPING ALL OVER INDIA😊*</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Code-1276, SAC, M66B, N175N, 9816034, No.9450, L 22inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0028.jpg</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -300rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>300</v>
+      </c>
+      <c r="F211" t="n">
+        <v>105</v>
+      </c>
+      <c r="G211" t="n">
+        <v>105</v>
+      </c>
+      <c r="H211" t="n">
+        <v>405</v>
+      </c>
+      <c r="I211" t="n">
+        <v>405</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -405rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Code-1277, SAC, MS6B, N1SON, 9811046, No.8350, 5 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0029.jpg</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -250rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>250</v>
+      </c>
+      <c r="F212" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G212" t="n">
+        <v>88</v>
+      </c>
+      <c r="H212" t="n">
+        <v>338</v>
+      </c>
+      <c r="I212" t="n">
+        <v>340</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -340rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Code-1278, A'C, M48A, N1ZSN, 678034, No.7300</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0030.jpg</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -250rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>250</v>
+      </c>
+      <c r="F213" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G213" t="n">
+        <v>88</v>
+      </c>
+      <c r="H213" t="n">
+        <v>338</v>
+      </c>
+      <c r="I213" t="n">
+        <v>340</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -340rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Code -1279, SAC, MABA, N125N, 568034, No.8300</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0031.jpg</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -300rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>300</v>
+      </c>
+      <c r="F214" t="n">
+        <v>105</v>
+      </c>
+      <c r="G214" t="n">
+        <v>105</v>
+      </c>
+      <c r="H214" t="n">
+        <v>405</v>
+      </c>
+      <c r="I214" t="n">
+        <v>405</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -405rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Code-1280, M56B, NISON, 8911045, No.8350</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0032.jpg</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -300rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>300</v>
+      </c>
+      <c r="F215" t="n">
+        <v>105</v>
+      </c>
+      <c r="G215" t="n">
+        <v>105</v>
+      </c>
+      <c r="H215" t="n">
+        <v>405</v>
+      </c>
+      <c r="I215" t="n">
+        <v>405</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>*✨ TRADITIONAL EARCUFF ✨* *Price -405rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>MS6B, Code-1281, NISON, SAC, 8911045, No.8350</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0033.jpg</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>*✨GOLD PLATED शिंदे शाही तोडे ✨* Size- 2.4, 2.6, 2.8 Price- 1250 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F216" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="G216" t="n">
+        <v>438</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1688</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>*✨GOLD PLATED शिंदे शाही तोडे ✨* Size- 2.4, 2.6, 2.8 Price- 1690 Rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Code-1282, SAC, M24OE, N625N, 6975041, No.61500</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0034.jpg</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -350rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>350</v>
+      </c>
+      <c r="F217" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G217" t="n">
+        <v>122</v>
+      </c>
+      <c r="H217" t="n">
+        <v>472</v>
+      </c>
+      <c r="I217" t="n">
+        <v>470</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -470rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>M68A, N1Z5N, Code-1283, SAC, 8916034, No.9420</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0035.jpg</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -350rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>350</v>
+      </c>
+      <c r="F218" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G218" t="n">
+        <v>122</v>
+      </c>
+      <c r="H218" t="n">
+        <v>472</v>
+      </c>
+      <c r="I218" t="n">
+        <v>470</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -470rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>M68A, Code-1285, N174N, SAC, 4514589, No.6420</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0036.jpg</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -320rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>320</v>
+      </c>
+      <c r="F219" t="n">
+        <v>112</v>
+      </c>
+      <c r="G219" t="n">
+        <v>112</v>
+      </c>
+      <c r="H219" t="n">
+        <v>432</v>
+      </c>
+      <c r="I219" t="n">
+        <v>430</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -430rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Code-1287, SAC, M62A, N16ON, 8913046, No.7400</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0037.jpg</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -330rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>330</v>
+      </c>
+      <c r="F220" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="G220" t="n">
+        <v>115</v>
+      </c>
+      <c r="H220" t="n">
+        <v>445</v>
+      </c>
+      <c r="I220" t="n">
+        <v>445</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -445rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Code-1287, SAC, M6SA, NI65N, 9813057, No.6400</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>IMG-20260325-WA0038.jpg</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -350rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>350</v>
+      </c>
+      <c r="F221" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G221" t="n">
+        <v>122</v>
+      </c>
+      <c r="H221" t="n">
+        <v>472</v>
+      </c>
+      <c r="I221" t="n">
+        <v>470</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>*✨ AD STONE HALF EARCUFF ✨* *Price -470rs FREE SHIPPING ALL OVER INDIA😊</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Code-1286, SAC, M68A, N1ZSN, 8916034, No.9420</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
